--- a/src/components/LugCalculator/Kn.xlsx
+++ b/src/components/LugCalculator/Kn.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\portfolio\src\components\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\portfolio\src\components\LugCalculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D6DC909-80F6-40C3-BB7C-0EC22BADE37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBDB3BA9-FB0A-440A-B01D-A26CEC15CA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{B86692AA-6AD1-4F17-95A9-760893952109}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B86692AA-6AD1-4F17-95A9-760893952109}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
   <si>
     <t>Fty_Ftu</t>
   </si>
@@ -53,6 +53,69 @@
   </si>
   <si>
     <t>Dw</t>
+  </si>
+  <si>
+    <t>0.00, 0.00</t>
+  </si>
+  <si>
+    <t>0.05, 0.05</t>
+  </si>
+  <si>
+    <t>0.10, 0.10</t>
+  </si>
+  <si>
+    <t>0.15, 0.15</t>
+  </si>
+  <si>
+    <t>0.20, 0.19</t>
+  </si>
+  <si>
+    <t>0.25, 0.24</t>
+  </si>
+  <si>
+    <t>0.30, 0.28</t>
+  </si>
+  <si>
+    <t>0.35, 0.31</t>
+  </si>
+  <si>
+    <t>0.40, 0.34</t>
+  </si>
+  <si>
+    <t>0.45, 0.37</t>
+  </si>
+  <si>
+    <t>0.50, 0.40</t>
+  </si>
+  <si>
+    <t>0.55, 0.43</t>
+  </si>
+  <si>
+    <t>0.60, 0.46</t>
+  </si>
+  <si>
+    <t>0.65, 0.50</t>
+  </si>
+  <si>
+    <t>0.70, 0.53</t>
+  </si>
+  <si>
+    <t>0.75, 0.58</t>
+  </si>
+  <si>
+    <t>0.80, 0.64</t>
+  </si>
+  <si>
+    <t>0.85, 0.71</t>
+  </si>
+  <si>
+    <t>0.90, 0.79</t>
+  </si>
+  <si>
+    <t>0.95, 0.88</t>
+  </si>
+  <si>
+    <t>1.00, 1.00</t>
   </si>
 </sst>
 </file>
@@ -94,8 +157,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -228,41 +292,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$4:$C$14</c:f>
+              <c:f>Sheet2!$C$4:$C$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -270,41 +364,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$D$4:$D$14</c:f>
+              <c:f>Sheet2!$D$4:$D$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.65</c:v>
-                </c:pt>
                 <c:pt idx="3">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>0.72</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.78</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.82</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="15">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -357,41 +481,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$4:$C$14</c:f>
+              <c:f>Sheet2!$C$4:$C$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -399,14 +553,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$E$4:$E$14</c:f>
+              <c:f>Sheet2!$E$4:$E$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.72</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -459,41 +670,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$4:$C$14</c:f>
+              <c:f>Sheet2!$C$4:$C$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -501,14 +742,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$F$4:$F$14</c:f>
+              <c:f>Sheet2!$F$4:$F$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.7</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -561,41 +859,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$4:$C$14</c:f>
+              <c:f>Sheet2!$C$4:$C$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -603,14 +931,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$G$4:$G$14</c:f>
+              <c:f>Sheet2!$G$4:$G$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.63</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -663,41 +1048,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$4:$C$14</c:f>
+              <c:f>Sheet2!$C$4:$C$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -705,14 +1120,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$H$4:$H$14</c:f>
+              <c:f>Sheet2!$H$4:$H$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.53</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -765,41 +1237,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$4:$C$14</c:f>
+              <c:f>Sheet2!$C$4:$C$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -807,14 +1309,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$I$4:$I$14</c:f>
+              <c:f>Sheet2!$I$4:$I$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.28999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.43</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.46</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -873,41 +1432,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$4:$C$14</c:f>
+              <c:f>Sheet2!$C$4:$C$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -915,41 +1504,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$J$4:$J$14</c:f>
+              <c:f>Sheet2!$J$4:$J$24</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.2</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.28000000000000003</c:v>
+                  <c:v>0.15</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.35</c:v>
+                  <c:v>0.19</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.45</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.52</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.65</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.78</c:v>
-                </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -981,7 +1600,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1044,7 +1663,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1277,41 +1896,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$15:$C$25</c:f>
+              <c:f>Sheet2!$C$25:$C$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1319,41 +1968,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$D$15:$D$25</c:f>
+              <c:f>Sheet2!$D$25:$D$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.65</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.82</c:v>
+                  <c:v>0.66</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.83</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.85</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.86</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>0.88</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="12">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="14">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.92</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.95</c:v>
-                </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="17">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1406,41 +2085,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$15:$C$25</c:f>
+              <c:f>Sheet2!$C$25:$C$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1448,14 +2157,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$E$15:$E$25</c:f>
+              <c:f>Sheet2!$E$25:$E$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.38</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.86</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1508,41 +2274,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$15:$C$25</c:f>
+              <c:f>Sheet2!$C$25:$C$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1550,14 +2346,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$F$15:$F$25</c:f>
+              <c:f>Sheet2!$F$25:$F$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.83</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1610,41 +2463,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$15:$C$25</c:f>
+              <c:f>Sheet2!$C$25:$C$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1652,14 +2535,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$G$15:$G$25</c:f>
+              <c:f>Sheet2!$G$25:$G$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.69</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1712,41 +2652,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$15:$C$25</c:f>
+              <c:f>Sheet2!$C$25:$C$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1754,14 +2724,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$H$15:$H$25</c:f>
+              <c:f>Sheet2!$H$25:$H$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.28999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1814,41 +2841,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$15:$C$25</c:f>
+              <c:f>Sheet2!$C$25:$C$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1856,14 +2913,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$I$15:$I$25</c:f>
+              <c:f>Sheet2!$I$25:$I$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.44</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1922,41 +3036,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$15:$C$25</c:f>
+              <c:f>Sheet2!$C$25:$C$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1964,41 +3108,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$J$15:$J$25</c:f>
+              <c:f>Sheet2!$J$25:$J$45</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.2</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3</c:v>
+                  <c:v>0.15</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.35</c:v>
+                  <c:v>0.19</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.45</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.52</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.65</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.78</c:v>
-                </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2030,7 +3204,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2093,7 +3267,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2326,41 +3500,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$26:$C$36</c:f>
+              <c:f>Sheet2!$C$46:$C$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2368,21 +3572,21 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$D$26:$D$36</c:f>
+              <c:f>Sheet2!$D$46:$D$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8</c:v>
+                  <c:v>0.54</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0.78</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0.93</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1</c:v>
@@ -2403,6 +3607,36 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2455,41 +3689,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$26:$C$36</c:f>
+              <c:f>Sheet2!$C$46:$C$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2497,14 +3761,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$E$26:$E$36</c:f>
+              <c:f>Sheet2!$E$46:$E$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2557,41 +3878,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$26:$C$36</c:f>
+              <c:f>Sheet2!$C$46:$C$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2599,14 +3950,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$F$26:$F$36</c:f>
+              <c:f>Sheet2!$F$46:$F$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.97</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2659,41 +4067,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$26:$C$36</c:f>
+              <c:f>Sheet2!$C$46:$C$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2701,14 +4139,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$G$26:$G$36</c:f>
+              <c:f>Sheet2!$G$46:$G$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.75</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2761,41 +4256,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$26:$C$36</c:f>
+              <c:f>Sheet2!$C$46:$C$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2803,14 +4328,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$H$26:$H$36</c:f>
+              <c:f>Sheet2!$H$46:$H$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2863,41 +4445,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$26:$C$36</c:f>
+              <c:f>Sheet2!$C$46:$C$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2905,14 +4517,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$I$26:$I$36</c:f>
+              <c:f>Sheet2!$I$46:$I$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2971,41 +4640,71 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$C$26:$C$36</c:f>
+              <c:f>Sheet2!$C$46:$C$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.3</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="9">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0.6</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>0.7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="15">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0.8</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="17">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.9</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3013,41 +4712,71 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$J$26:$J$36</c:f>
+              <c:f>Sheet2!$J$46:$J$66</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0.28000000000000003</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.4</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.45</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.52</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.62</c:v>
-                </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.46</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.78</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="19">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3079,7 +4808,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3142,7 +4871,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4893,16 +6622,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>302745</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>48191</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>478453</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>175265</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>605678</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>29141</xdr:rowOff>
+      <xdr:colOff>164838</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>146690</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4929,16 +6658,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>228039</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>107956</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>538218</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>68623</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>530972</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>88905</xdr:rowOff>
+      <xdr:colOff>226509</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>68622</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4966,15 +6695,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>250450</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>78074</xdr:rowOff>
+      <xdr:colOff>235434</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>66868</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>553383</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>59023</xdr:rowOff>
+      <xdr:colOff>538367</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>44007</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5300,9 +7029,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FDAB996-2757-4CDA-BD6E-70BABBDD6CAD}">
   <dimension ref="A5:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>B5^-1/2</f>
         <v>3.3333333333333335</v>
@@ -5314,7 +7043,7 @@
         <v>8.5069999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" ref="A6:A14" si="0">B6^-1/2</f>
         <v>2.5</v>
@@ -5326,7 +7055,7 @@
         <v>6.907</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -5338,7 +7067,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>1.6666666666666667</v>
@@ -5350,7 +7079,7 @@
         <v>5.4029999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>1.4285714285714286</v>
@@ -5362,7 +7091,7 @@
         <v>5.0380000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>1.25</v>
@@ -5374,7 +7103,7 @@
         <v>4.8170000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>1.1111111111111112</v>
@@ -5386,7 +7115,7 @@
         <v>4.7069999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -5398,7 +7127,7 @@
         <v>4.6920000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>0.90909090909090906</v>
@@ -5410,7 +7139,7 @@
         <v>4.7690000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>0.83333333333333337</v>
@@ -5429,14 +7158,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DED8BC0-7630-4FEC-A3D6-F44AF91D8DCF}">
-  <dimension ref="B3:J36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:M138"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="9" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="M2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -5464,556 +7197,3753 @@
       <c r="J3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B4">
+      <c r="M3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
         <v>0.6</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>0</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>0</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>0</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>0</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>0</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>0</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B5">
+      <c r="M4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
         <v>0.6</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="I5" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="M5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C6" s="1">
         <v>0.1</v>
       </c>
-      <c r="D5">
+      <c r="D6" s="1">
         <v>0.5</v>
       </c>
-      <c r="J5">
+      <c r="E6" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J6" s="1">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B6">
+      <c r="M6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
         <v>0.6</v>
       </c>
-      <c r="C6">
+      <c r="C7" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="M7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="1">
         <v>0.2</v>
       </c>
-      <c r="D6">
+      <c r="D8" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="E8" s="1">
         <v>0.65</v>
       </c>
-      <c r="J6">
+      <c r="F8" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="M8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="M9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="M10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="M11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="M12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="M13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="M15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B16" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="M16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B17" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.79</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="M17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B18" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.82</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="M18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B19" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.82</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="M19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B20" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="M20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B21" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="M21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B22" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0.79</v>
+      </c>
+      <c r="M22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B23" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B24" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B25" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B26" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="I26" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B27" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B28" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.79</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B29" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C29" s="1">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B7">
+      <c r="D29" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B30" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B31" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B32" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0.48</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B33" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B34" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B35" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B36" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B37" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C37" s="1">
         <v>0.6</v>
       </c>
-      <c r="C7">
+      <c r="D37" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B38" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.79</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B39" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.82</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B40" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B41" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B42" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0.79</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B43" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B44" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B45" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1">
+        <v>1</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B46" s="1">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B47" s="1">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="I47" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B48" s="1">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B49" s="1">
+        <v>1</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0.93</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="J49" s="1">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B50" s="1">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D50" s="1">
+        <v>1</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="H50" s="1">
         <v>0.3</v>
       </c>
-      <c r="D7">
+      <c r="I50" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B51" s="1">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B52" s="1">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B53" s="1">
+        <v>1</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0.93</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0.48</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B54" s="1">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="J54" s="1">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B55" s="1">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="J55" s="1">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B56" s="1">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B57" s="1">
+        <v>1</v>
+      </c>
+      <c r="C57" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B58" s="1">
+        <v>1</v>
+      </c>
+      <c r="C58" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B59" s="1">
+        <v>1</v>
+      </c>
+      <c r="C59" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="I59" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="J59" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B60" s="1">
+        <v>1</v>
+      </c>
+      <c r="C60" s="1">
         <v>0.7</v>
       </c>
-      <c r="J7">
+      <c r="D60" s="1">
+        <v>1</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B61" s="1">
+        <v>1</v>
+      </c>
+      <c r="C61" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0.93</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="I61" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="J61" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B62" s="1">
+        <v>1</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="1">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B63" s="1">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="I63" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="J63" s="1">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B64" s="1">
+        <v>1</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="I64" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="J64" s="1">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B65" s="1">
+        <v>1</v>
+      </c>
+      <c r="C65" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="1">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I65" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B66" s="1">
+        <v>1</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="1">
+        <v>1</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1</v>
+      </c>
+      <c r="I66" s="1">
+        <v>1</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B70" t="str">
+        <f>_xlfn.CONCAT(B$3,": ",B4,", ")</f>
+        <v xml:space="preserve">Fty_Ftu: 0.6, </v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>2</v>
+      </c>
+      <c r="F75" t="s">
+        <v>3</v>
+      </c>
+      <c r="G75" t="s">
+        <v>4</v>
+      </c>
+      <c r="H75" t="s">
+        <v>5</v>
+      </c>
+      <c r="I75" t="s">
+        <v>6</v>
+      </c>
+      <c r="J75" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B76">
+        <v>0.6</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B77">
+        <v>0.6</v>
+      </c>
+      <c r="C77">
+        <v>0.05</v>
+      </c>
+      <c r="D77">
+        <v>0.33</v>
+      </c>
+      <c r="E77">
+        <v>0.33</v>
+      </c>
+      <c r="F77">
+        <v>0.26</v>
+      </c>
+      <c r="G77">
+        <v>0.15</v>
+      </c>
+      <c r="H77">
+        <v>0.09</v>
+      </c>
+      <c r="I77">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J77">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B78">
+        <v>0.6</v>
+      </c>
+      <c r="C78">
+        <v>0.1</v>
+      </c>
+      <c r="D78">
+        <v>0.5</v>
+      </c>
+      <c r="E78">
+        <v>0.49</v>
+      </c>
+      <c r="F78">
+        <v>0.41</v>
+      </c>
+      <c r="G78">
+        <v>0.24</v>
+      </c>
+      <c r="H78">
+        <v>0.16</v>
+      </c>
+      <c r="I78">
+        <v>0.12</v>
+      </c>
+      <c r="J78">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B79">
+        <v>0.6</v>
+      </c>
+      <c r="C79">
+        <v>0.15</v>
+      </c>
+      <c r="D79">
+        <v>0.61</v>
+      </c>
+      <c r="E79">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F79">
+        <v>0.52</v>
+      </c>
+      <c r="G79">
+        <v>0.32</v>
+      </c>
+      <c r="H79">
+        <v>0.22</v>
+      </c>
+      <c r="I79">
+        <v>0.18</v>
+      </c>
+      <c r="J79">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B80">
+        <v>0.6</v>
+      </c>
+      <c r="C80">
+        <v>0.2</v>
+      </c>
+      <c r="D80">
+        <v>0.67</v>
+      </c>
+      <c r="E80">
+        <v>0.65</v>
+      </c>
+      <c r="F80">
+        <v>0.59</v>
+      </c>
+      <c r="G80">
+        <v>0.4</v>
+      </c>
+      <c r="H80">
+        <v>0.3</v>
+      </c>
+      <c r="I80">
+        <v>0.24</v>
+      </c>
+      <c r="J80">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B81">
+        <v>0.6</v>
+      </c>
+      <c r="C81">
+        <v>0.25</v>
+      </c>
+      <c r="D81">
+        <v>0.7</v>
+      </c>
+      <c r="E81">
+        <v>0.68</v>
+      </c>
+      <c r="F81">
+        <v>0.63</v>
+      </c>
+      <c r="G81">
+        <v>0.47</v>
+      </c>
+      <c r="H81">
+        <v>0.36</v>
+      </c>
+      <c r="I81">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J81">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B82">
+        <v>0.6</v>
+      </c>
+      <c r="C82">
+        <v>0.3</v>
+      </c>
+      <c r="D82">
+        <v>0.71</v>
+      </c>
+      <c r="E82">
+        <v>0.69</v>
+      </c>
+      <c r="F82">
+        <v>0.66</v>
+      </c>
+      <c r="G82">
+        <v>0.53</v>
+      </c>
+      <c r="H82">
+        <v>0.41</v>
+      </c>
+      <c r="I82">
+        <v>0.33</v>
+      </c>
+      <c r="J82">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B83">
+        <v>0.6</v>
+      </c>
+      <c r="C83">
+        <v>0.35</v>
+      </c>
+      <c r="D83">
+        <v>0.72</v>
+      </c>
+      <c r="E83">
+        <v>0.7</v>
+      </c>
+      <c r="F83">
+        <v>0.68</v>
+      </c>
+      <c r="G83">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H83">
+        <v>0.45</v>
+      </c>
+      <c r="I83">
+        <v>0.37</v>
+      </c>
+      <c r="J83">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B84">
+        <v>0.6</v>
+      </c>
+      <c r="C84">
+        <v>0.4</v>
+      </c>
+      <c r="D84">
+        <v>0.73</v>
+      </c>
+      <c r="E84">
+        <v>0.71</v>
+      </c>
+      <c r="F84">
+        <v>0.69</v>
+      </c>
+      <c r="G84">
+        <v>0.61</v>
+      </c>
+      <c r="H84">
+        <v>0.49</v>
+      </c>
+      <c r="I84">
+        <v>0.4</v>
+      </c>
+      <c r="J84">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B85">
+        <v>0.6</v>
+      </c>
+      <c r="C85">
+        <v>0.45</v>
+      </c>
+      <c r="D85">
+        <v>0.74</v>
+      </c>
+      <c r="E85">
+        <v>0.72</v>
+      </c>
+      <c r="F85">
+        <v>0.7</v>
+      </c>
+      <c r="G85">
+        <v>0.63</v>
+      </c>
+      <c r="H85">
+        <v>0.53</v>
+      </c>
+      <c r="I85">
+        <v>0.43</v>
+      </c>
+      <c r="J85">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B86">
+        <v>0.6</v>
+      </c>
+      <c r="C86">
+        <v>0.5</v>
+      </c>
+      <c r="D86">
+        <v>0.76</v>
+      </c>
+      <c r="E86">
+        <v>0.74</v>
+      </c>
+      <c r="F86">
+        <v>0.72</v>
+      </c>
+      <c r="G86">
+        <v>0.64</v>
+      </c>
+      <c r="H86">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I86">
+        <v>0.46</v>
+      </c>
+      <c r="J86">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B87">
+        <v>0.6</v>
+      </c>
+      <c r="C87">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D87">
+        <v>0.77</v>
+      </c>
+      <c r="E87">
+        <v>0.76</v>
+      </c>
+      <c r="F87">
+        <v>0.73</v>
+      </c>
+      <c r="G87">
+        <v>0.66</v>
+      </c>
+      <c r="H87">
+        <v>0.59</v>
+      </c>
+      <c r="I87">
+        <v>0.5</v>
+      </c>
+      <c r="J87">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B88">
+        <v>0.6</v>
+      </c>
+      <c r="C88">
+        <v>0.6</v>
+      </c>
+      <c r="D88">
+        <v>0.78</v>
+      </c>
+      <c r="E88">
+        <v>0.77</v>
+      </c>
+      <c r="F88">
+        <v>0.74</v>
+      </c>
+      <c r="G88">
+        <v>0.68</v>
+      </c>
+      <c r="H88">
+        <v>0.62</v>
+      </c>
+      <c r="I88">
+        <v>0.53</v>
+      </c>
+      <c r="J88">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B89">
+        <v>0.6</v>
+      </c>
+      <c r="C89">
+        <v>0.65</v>
+      </c>
+      <c r="D89">
+        <v>0.8</v>
+      </c>
+      <c r="E89">
+        <v>0.79</v>
+      </c>
+      <c r="F89">
+        <v>0.77</v>
+      </c>
+      <c r="G89">
+        <v>0.7</v>
+      </c>
+      <c r="H89">
+        <v>0.64</v>
+      </c>
+      <c r="I89">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J89">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B90">
+        <v>0.6</v>
+      </c>
+      <c r="C90">
+        <v>0.7</v>
+      </c>
+      <c r="D90">
+        <v>0.82</v>
+      </c>
+      <c r="E90">
+        <v>0.81</v>
+      </c>
+      <c r="F90">
+        <v>0.78</v>
+      </c>
+      <c r="G90">
+        <v>0.73</v>
+      </c>
+      <c r="H90">
+        <v>0.68</v>
+      </c>
+      <c r="I90">
+        <v>0.61</v>
+      </c>
+      <c r="J90">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B91">
+        <v>0.6</v>
+      </c>
+      <c r="C91">
+        <v>0.75</v>
+      </c>
+      <c r="D91">
+        <v>0.84</v>
+      </c>
+      <c r="E91">
+        <v>0.82</v>
+      </c>
+      <c r="F91">
+        <v>0.81</v>
+      </c>
+      <c r="G91">
+        <v>0.77</v>
+      </c>
+      <c r="H91">
+        <v>0.72</v>
+      </c>
+      <c r="I91">
+        <v>0.66</v>
+      </c>
+      <c r="J91">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B92">
+        <v>0.6</v>
+      </c>
+      <c r="C92">
+        <v>0.8</v>
+      </c>
+      <c r="D92">
+        <v>0.86</v>
+      </c>
+      <c r="E92">
+        <v>0.84</v>
+      </c>
+      <c r="F92">
+        <v>0.84</v>
+      </c>
+      <c r="G92">
+        <v>0.8</v>
+      </c>
+      <c r="H92">
+        <v>0.76</v>
+      </c>
+      <c r="I92">
+        <v>0.71</v>
+      </c>
+      <c r="J92">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B93">
+        <v>0.6</v>
+      </c>
+      <c r="C93">
+        <v>0.85</v>
+      </c>
+      <c r="D93">
+        <v>0.88</v>
+      </c>
+      <c r="E93">
+        <v>0.87</v>
+      </c>
+      <c r="F93">
+        <v>0.87</v>
+      </c>
+      <c r="G93">
+        <v>0.84</v>
+      </c>
+      <c r="H93">
+        <v>0.81</v>
+      </c>
+      <c r="I93">
+        <v>0.77</v>
+      </c>
+      <c r="J93">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B94">
+        <v>0.6</v>
+      </c>
+      <c r="C94">
+        <v>0.9</v>
+      </c>
+      <c r="D94">
+        <v>0.91</v>
+      </c>
+      <c r="E94">
+        <v>0.9</v>
+      </c>
+      <c r="F94">
+        <v>0.9</v>
+      </c>
+      <c r="G94">
+        <v>0.88</v>
+      </c>
+      <c r="H94">
+        <v>0.86</v>
+      </c>
+      <c r="I94">
+        <v>0.83</v>
+      </c>
+      <c r="J94">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B95">
+        <v>0.6</v>
+      </c>
+      <c r="C95">
+        <v>0.95</v>
+      </c>
+      <c r="D95">
+        <v>0.95</v>
+      </c>
+      <c r="E95">
+        <v>0.95</v>
+      </c>
+      <c r="F95">
+        <v>0.95</v>
+      </c>
+      <c r="G95">
+        <v>0.94</v>
+      </c>
+      <c r="H95">
+        <v>0.94</v>
+      </c>
+      <c r="I95">
+        <v>0.92</v>
+      </c>
+      <c r="J95">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B96">
+        <v>0.6</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B97">
+        <v>0.8</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B98">
+        <v>0.8</v>
+      </c>
+      <c r="C98">
+        <v>0.05</v>
+      </c>
+      <c r="D98">
+        <v>0.4</v>
+      </c>
+      <c r="E98">
+        <v>0.38</v>
+      </c>
+      <c r="F98">
+        <v>0.24</v>
+      </c>
+      <c r="G98">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H98">
+        <v>0.08</v>
+      </c>
+      <c r="I98">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J98">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B99">
+        <v>0.8</v>
+      </c>
+      <c r="C99">
+        <v>0.1</v>
+      </c>
+      <c r="D99">
+        <v>0.66</v>
+      </c>
+      <c r="E99">
+        <v>0.59</v>
+      </c>
+      <c r="F99">
+        <v>0.42</v>
+      </c>
+      <c r="G99">
+        <v>0.25</v>
+      </c>
+      <c r="H99">
+        <v>0.15</v>
+      </c>
+      <c r="I99">
+        <v>0.12</v>
+      </c>
+      <c r="J99">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B100">
+        <v>0.8</v>
+      </c>
+      <c r="C100">
+        <v>0.15</v>
+      </c>
+      <c r="D100">
+        <v>0.79</v>
+      </c>
+      <c r="E100">
+        <v>0.73</v>
+      </c>
+      <c r="F100">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G100">
+        <v>0.35</v>
+      </c>
+      <c r="H100">
+        <v>0.22</v>
+      </c>
+      <c r="I100">
+        <v>0.18</v>
+      </c>
+      <c r="J100">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B101">
+        <v>0.8</v>
+      </c>
+      <c r="C101">
+        <v>0.2</v>
+      </c>
+      <c r="D101">
+        <v>0.83</v>
+      </c>
+      <c r="E101">
+        <v>0.81</v>
+      </c>
+      <c r="F101">
+        <v>0.67</v>
+      </c>
+      <c r="G101">
+        <v>0.43</v>
+      </c>
+      <c r="H101">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I101">
+        <v>0.23</v>
+      </c>
+      <c r="J101">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B102">
+        <v>0.8</v>
+      </c>
+      <c r="C102">
+        <v>0.25</v>
+      </c>
+      <c r="D102">
+        <v>0.84</v>
+      </c>
+      <c r="E102">
+        <v>0.83</v>
+      </c>
+      <c r="F102">
+        <v>0.74</v>
+      </c>
+      <c r="G102">
+        <v>0.5</v>
+      </c>
+      <c r="H102">
+        <v>0.36</v>
+      </c>
+      <c r="I102">
         <v>0.28000000000000003</v>
       </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B8">
+      <c r="J102">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B103">
+        <v>0.8</v>
+      </c>
+      <c r="C103">
+        <v>0.3</v>
+      </c>
+      <c r="D103">
+        <v>0.85</v>
+      </c>
+      <c r="E103">
+        <v>0.84</v>
+      </c>
+      <c r="F103">
+        <v>0.77</v>
+      </c>
+      <c r="G103">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H103">
+        <v>0.42</v>
+      </c>
+      <c r="I103">
+        <v>0.33</v>
+      </c>
+      <c r="J103">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B104">
+        <v>0.8</v>
+      </c>
+      <c r="C104">
+        <v>0.35</v>
+      </c>
+      <c r="D104">
+        <v>0.85</v>
+      </c>
+      <c r="E104">
+        <v>0.85</v>
+      </c>
+      <c r="F104">
+        <v>0.8</v>
+      </c>
+      <c r="G104">
+        <v>0.62</v>
+      </c>
+      <c r="H104">
+        <v>0.48</v>
+      </c>
+      <c r="I104">
+        <v>0.37</v>
+      </c>
+      <c r="J104">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B105">
+        <v>0.8</v>
+      </c>
+      <c r="C105">
+        <v>0.4</v>
+      </c>
+      <c r="D105">
+        <v>0.86</v>
+      </c>
+      <c r="E105">
+        <v>0.86</v>
+      </c>
+      <c r="F105">
+        <v>0.81</v>
+      </c>
+      <c r="G105">
+        <v>0.66</v>
+      </c>
+      <c r="H105">
+        <v>0.52</v>
+      </c>
+      <c r="I105">
+        <v>0.41</v>
+      </c>
+      <c r="J105">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B106">
+        <v>0.8</v>
+      </c>
+      <c r="C106">
+        <v>0.45</v>
+      </c>
+      <c r="D106">
+        <v>0.86</v>
+      </c>
+      <c r="E106">
+        <v>0.86</v>
+      </c>
+      <c r="F106">
+        <v>0.83</v>
+      </c>
+      <c r="G106">
+        <v>0.69</v>
+      </c>
+      <c r="H106">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I106">
+        <v>0.44</v>
+      </c>
+      <c r="J106">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B107">
+        <v>0.8</v>
+      </c>
+      <c r="C107">
+        <v>0.5</v>
+      </c>
+      <c r="D107">
+        <v>0.87</v>
+      </c>
+      <c r="E107">
+        <v>0.87</v>
+      </c>
+      <c r="F107">
+        <v>0.84</v>
+      </c>
+      <c r="G107">
+        <v>0.72</v>
+      </c>
+      <c r="H107">
+        <v>0.59</v>
+      </c>
+      <c r="I107">
+        <v>0.47</v>
+      </c>
+      <c r="J107">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B108">
+        <v>0.8</v>
+      </c>
+      <c r="C108">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D108">
+        <v>0.88</v>
+      </c>
+      <c r="E108">
+        <v>0.88</v>
+      </c>
+      <c r="F108">
+        <v>0.84</v>
+      </c>
+      <c r="G108">
+        <v>0.74</v>
+      </c>
+      <c r="H108">
+        <v>0.62</v>
+      </c>
+      <c r="I108">
+        <v>0.51</v>
+      </c>
+      <c r="J108">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B109">
+        <v>0.8</v>
+      </c>
+      <c r="C109">
         <v>0.6</v>
       </c>
-      <c r="C8">
+      <c r="D109">
+        <v>0.89</v>
+      </c>
+      <c r="E109">
+        <v>0.89</v>
+      </c>
+      <c r="F109">
+        <v>0.85</v>
+      </c>
+      <c r="G109">
+        <v>0.76</v>
+      </c>
+      <c r="H109">
+        <v>0.65</v>
+      </c>
+      <c r="I109">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J109">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B110">
+        <v>0.8</v>
+      </c>
+      <c r="C110">
+        <v>0.65</v>
+      </c>
+      <c r="D110">
+        <v>0.9</v>
+      </c>
+      <c r="E110">
+        <v>0.9</v>
+      </c>
+      <c r="F110">
+        <v>0.86</v>
+      </c>
+      <c r="G110">
+        <v>0.79</v>
+      </c>
+      <c r="H110">
+        <v>0.68</v>
+      </c>
+      <c r="I110">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J110">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B111">
+        <v>0.8</v>
+      </c>
+      <c r="C111">
+        <v>0.7</v>
+      </c>
+      <c r="D111">
+        <v>0.9</v>
+      </c>
+      <c r="E111">
+        <v>0.9</v>
+      </c>
+      <c r="F111">
+        <v>0.87</v>
+      </c>
+      <c r="G111">
+        <v>0.82</v>
+      </c>
+      <c r="H111">
+        <v>0.72</v>
+      </c>
+      <c r="I111">
+        <v>0.63</v>
+      </c>
+      <c r="J111">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B112">
+        <v>0.8</v>
+      </c>
+      <c r="C112">
+        <v>0.75</v>
+      </c>
+      <c r="D112">
+        <v>0.91</v>
+      </c>
+      <c r="E112">
+        <v>0.91</v>
+      </c>
+      <c r="F112">
+        <v>0.89</v>
+      </c>
+      <c r="G112">
+        <v>0.84</v>
+      </c>
+      <c r="H112">
+        <v>0.77</v>
+      </c>
+      <c r="I112">
+        <v>0.69</v>
+      </c>
+      <c r="J112">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B113">
+        <v>0.8</v>
+      </c>
+      <c r="C113">
+        <v>0.8</v>
+      </c>
+      <c r="D113">
+        <v>0.92</v>
+      </c>
+      <c r="E113">
+        <v>0.92</v>
+      </c>
+      <c r="F113">
+        <v>0.92</v>
+      </c>
+      <c r="G113">
+        <v>0.88</v>
+      </c>
+      <c r="H113">
+        <v>0.83</v>
+      </c>
+      <c r="I113">
+        <v>0.74</v>
+      </c>
+      <c r="J113">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B114">
+        <v>0.8</v>
+      </c>
+      <c r="C114">
+        <v>0.85</v>
+      </c>
+      <c r="D114">
+        <v>0.94</v>
+      </c>
+      <c r="E114">
+        <v>0.94</v>
+      </c>
+      <c r="F114">
+        <v>0.94</v>
+      </c>
+      <c r="G114">
+        <v>0.91</v>
+      </c>
+      <c r="H114">
+        <v>0.87</v>
+      </c>
+      <c r="I114">
+        <v>0.79</v>
+      </c>
+      <c r="J114">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="115" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B115">
+        <v>0.8</v>
+      </c>
+      <c r="C115">
+        <v>0.9</v>
+      </c>
+      <c r="D115">
+        <v>0.96</v>
+      </c>
+      <c r="E115">
+        <v>0.96</v>
+      </c>
+      <c r="F115">
+        <v>0.96</v>
+      </c>
+      <c r="G115">
+        <v>0.94</v>
+      </c>
+      <c r="H115">
+        <v>0.91</v>
+      </c>
+      <c r="I115">
+        <v>0.85</v>
+      </c>
+      <c r="J115">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B116">
+        <v>0.8</v>
+      </c>
+      <c r="C116">
+        <v>0.95</v>
+      </c>
+      <c r="D116">
+        <v>0.97</v>
+      </c>
+      <c r="E116">
+        <v>0.97</v>
+      </c>
+      <c r="F116">
+        <v>0.97</v>
+      </c>
+      <c r="G116">
+        <v>0.97</v>
+      </c>
+      <c r="H116">
+        <v>0.95</v>
+      </c>
+      <c r="I116">
+        <v>0.92</v>
+      </c>
+      <c r="J116">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="117" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B117">
+        <v>0.8</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+      <c r="E117">
+        <v>1</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117">
+        <v>1</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119">
+        <v>0.05</v>
+      </c>
+      <c r="D119">
+        <v>0.54</v>
+      </c>
+      <c r="E119">
+        <v>0.44</v>
+      </c>
+      <c r="F119">
+        <v>0.26</v>
+      </c>
+      <c r="G119">
+        <v>0.13</v>
+      </c>
+      <c r="H119">
+        <v>0.09</v>
+      </c>
+      <c r="I119">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J119">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="120" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="C120">
+        <v>0.1</v>
+      </c>
+      <c r="D120">
+        <v>0.78</v>
+      </c>
+      <c r="E120">
+        <v>0.69</v>
+      </c>
+      <c r="F120">
+        <v>0.44</v>
+      </c>
+      <c r="G120">
+        <v>0.22</v>
+      </c>
+      <c r="H120">
+        <v>0.16</v>
+      </c>
+      <c r="I120">
+        <v>0.13</v>
+      </c>
+      <c r="J120">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="121" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B121">
+        <v>1</v>
+      </c>
+      <c r="C121">
+        <v>0.15</v>
+      </c>
+      <c r="D121">
+        <v>0.93</v>
+      </c>
+      <c r="E121">
+        <v>0.86</v>
+      </c>
+      <c r="F121">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G121">
+        <v>0.31</v>
+      </c>
+      <c r="H121">
+        <v>0.23</v>
+      </c>
+      <c r="I121">
+        <v>0.18</v>
+      </c>
+      <c r="J121">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="122" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122">
+        <v>0.2</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+      <c r="E122">
+        <v>0.96</v>
+      </c>
+      <c r="F122">
+        <v>0.71</v>
+      </c>
+      <c r="G122">
+        <v>0.42</v>
+      </c>
+      <c r="H122">
+        <v>0.3</v>
+      </c>
+      <c r="I122">
+        <v>0.23</v>
+      </c>
+      <c r="J122">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="123" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123">
+        <v>0.25</v>
+      </c>
+      <c r="D123">
+        <v>1</v>
+      </c>
+      <c r="E123">
+        <v>0.98</v>
+      </c>
+      <c r="F123">
+        <v>0.8</v>
+      </c>
+      <c r="G123">
+        <v>0.5</v>
+      </c>
+      <c r="H123">
+        <v>0.36</v>
+      </c>
+      <c r="I123">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J123">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="124" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B124">
+        <v>1</v>
+      </c>
+      <c r="C124">
+        <v>0.3</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
+      <c r="E124">
+        <v>0.99</v>
+      </c>
+      <c r="F124">
+        <v>0.87</v>
+      </c>
+      <c r="G124">
+        <v>0.6</v>
+      </c>
+      <c r="H124">
+        <v>0.42</v>
+      </c>
+      <c r="I124">
+        <v>0.33</v>
+      </c>
+      <c r="J124">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="125" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125">
+        <v>0.35</v>
+      </c>
+      <c r="D125">
+        <v>1</v>
+      </c>
+      <c r="E125">
+        <v>0.99</v>
+      </c>
+      <c r="F125">
+        <v>0.93</v>
+      </c>
+      <c r="G125">
+        <v>0.66</v>
+      </c>
+      <c r="H125">
+        <v>0.48</v>
+      </c>
+      <c r="I125">
+        <v>0.37</v>
+      </c>
+      <c r="J125">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="126" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126">
         <v>0.4</v>
       </c>
-      <c r="D8">
-        <v>0.72</v>
-      </c>
-      <c r="J8">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B9">
+      <c r="D126">
+        <v>1</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+      <c r="F126">
+        <v>0.96</v>
+      </c>
+      <c r="G126">
+        <v>0.71</v>
+      </c>
+      <c r="H126">
+        <v>0.53</v>
+      </c>
+      <c r="I126">
+        <v>0.41</v>
+      </c>
+      <c r="J126">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="127" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127">
+        <v>0.45</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+      <c r="E127">
+        <v>1</v>
+      </c>
+      <c r="F127">
+        <v>0.97</v>
+      </c>
+      <c r="G127">
+        <v>0.75</v>
+      </c>
+      <c r="H127">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I127">
+        <v>0.45</v>
+      </c>
+      <c r="J127">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="128" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B128">
+        <v>1</v>
+      </c>
+      <c r="C128">
+        <v>0.5</v>
+      </c>
+      <c r="D128">
+        <v>1</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+      <c r="F128">
+        <v>0.96</v>
+      </c>
+      <c r="G128">
+        <v>0.78</v>
+      </c>
+      <c r="H128">
+        <v>0.62</v>
+      </c>
+      <c r="I128">
+        <v>0.49</v>
+      </c>
+      <c r="J128">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="129" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B129">
+        <v>1</v>
+      </c>
+      <c r="C129">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+      <c r="E129">
+        <v>1</v>
+      </c>
+      <c r="F129">
+        <v>0.96</v>
+      </c>
+      <c r="G129">
+        <v>0.8</v>
+      </c>
+      <c r="H129">
+        <v>0.66</v>
+      </c>
+      <c r="I129">
+        <v>0.53</v>
+      </c>
+      <c r="J129">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130">
         <v>0.6</v>
       </c>
-      <c r="C9">
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="E130">
+        <v>1</v>
+      </c>
+      <c r="F130">
+        <v>0.96</v>
+      </c>
+      <c r="G130">
+        <v>0.83</v>
+      </c>
+      <c r="H130">
+        <v>0.69</v>
+      </c>
+      <c r="I130">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J130">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131">
+        <v>0.65</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131">
+        <v>1</v>
+      </c>
+      <c r="F131">
+        <v>0.96</v>
+      </c>
+      <c r="G131">
+        <v>0.87</v>
+      </c>
+      <c r="H131">
+        <v>0.73</v>
+      </c>
+      <c r="I131">
+        <v>0.6</v>
+      </c>
+      <c r="J131">
         <v>0.5</v>
       </c>
-      <c r="D9">
+    </row>
+    <row r="132" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B132">
+        <v>1</v>
+      </c>
+      <c r="C132">
+        <v>0.7</v>
+      </c>
+      <c r="D132">
+        <v>1</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+      <c r="F132">
+        <v>0.97</v>
+      </c>
+      <c r="G132">
+        <v>0.9</v>
+      </c>
+      <c r="H132">
+        <v>0.78</v>
+      </c>
+      <c r="I132">
+        <v>0.64</v>
+      </c>
+      <c r="J132">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="133" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B133">
+        <v>1</v>
+      </c>
+      <c r="C133">
         <v>0.75</v>
       </c>
-      <c r="J9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B10">
-        <v>0.6</v>
-      </c>
-      <c r="C10">
-        <v>0.6</v>
-      </c>
-      <c r="D10">
+      <c r="D133">
+        <v>1</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+      <c r="F133">
+        <v>0.99</v>
+      </c>
+      <c r="G133">
+        <v>0.93</v>
+      </c>
+      <c r="H133">
+        <v>0.84</v>
+      </c>
+      <c r="I133">
+        <v>0.7</v>
+      </c>
+      <c r="J133">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134">
+        <v>0.8</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134">
+        <v>0.97</v>
+      </c>
+      <c r="H134">
+        <v>0.91</v>
+      </c>
+      <c r="I134">
+        <v>0.76</v>
+      </c>
+      <c r="J134">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="135" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="C135">
+        <v>0.85</v>
+      </c>
+      <c r="D135">
+        <v>1</v>
+      </c>
+      <c r="E135">
+        <v>1</v>
+      </c>
+      <c r="F135">
+        <v>0.99</v>
+      </c>
+      <c r="G135">
+        <v>0.99</v>
+      </c>
+      <c r="H135">
+        <v>0.94</v>
+      </c>
+      <c r="I135">
+        <v>0.81</v>
+      </c>
+      <c r="J135">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="136" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B136">
+        <v>1</v>
+      </c>
+      <c r="C136">
+        <v>0.9</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>1</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136">
+        <v>1</v>
+      </c>
+      <c r="H136">
+        <v>0.97</v>
+      </c>
+      <c r="I136">
+        <v>0.86</v>
+      </c>
+      <c r="J136">
         <v>0.78</v>
       </c>
-      <c r="J10">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B11">
-        <v>0.6</v>
-      </c>
-      <c r="C11">
-        <v>0.7</v>
-      </c>
-      <c r="D11">
-        <v>0.82</v>
-      </c>
-      <c r="J11">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B12">
-        <v>0.6</v>
-      </c>
-      <c r="C12">
-        <v>0.8</v>
-      </c>
-      <c r="D12">
-        <v>0.85</v>
-      </c>
-      <c r="J12">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B13">
-        <v>0.6</v>
-      </c>
-      <c r="C13">
-        <v>0.9</v>
-      </c>
-      <c r="D13">
-        <v>0.9</v>
-      </c>
-      <c r="J13">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B14">
-        <v>0.6</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B15">
-        <v>0.8</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B16">
-        <v>0.8</v>
-      </c>
-      <c r="C16">
-        <v>0.1</v>
-      </c>
-      <c r="D16">
-        <v>0.65</v>
-      </c>
-      <c r="J16">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B17">
-        <v>0.8</v>
-      </c>
-      <c r="C17">
-        <v>0.2</v>
-      </c>
-      <c r="D17">
-        <v>0.82</v>
-      </c>
-      <c r="J17">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B18">
-        <v>0.8</v>
-      </c>
-      <c r="C18">
-        <v>0.3</v>
-      </c>
-      <c r="D18">
-        <v>0.83</v>
-      </c>
-      <c r="J18">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B19">
-        <v>0.8</v>
-      </c>
-      <c r="C19">
-        <v>0.4</v>
-      </c>
-      <c r="D19">
-        <v>0.85</v>
-      </c>
-      <c r="J19">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B20">
-        <v>0.8</v>
-      </c>
-      <c r="C20">
-        <v>0.5</v>
-      </c>
-      <c r="D20">
-        <v>0.86</v>
-      </c>
-      <c r="J20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B21">
-        <v>0.8</v>
-      </c>
-      <c r="C21">
-        <v>0.6</v>
-      </c>
-      <c r="D21">
-        <v>0.88</v>
-      </c>
-      <c r="J21">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B22">
-        <v>0.8</v>
-      </c>
-      <c r="C22">
-        <v>0.7</v>
-      </c>
-      <c r="D22">
-        <v>0.9</v>
-      </c>
-      <c r="J22">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B23">
-        <v>0.8</v>
-      </c>
-      <c r="C23">
-        <v>0.8</v>
-      </c>
-      <c r="D23">
+    </row>
+    <row r="137" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B137">
+        <v>1</v>
+      </c>
+      <c r="C137">
+        <v>0.95</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>1</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+      <c r="H137">
+        <v>0.99</v>
+      </c>
+      <c r="I137">
         <v>0.92</v>
       </c>
-      <c r="J23">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B24">
-        <v>0.8</v>
-      </c>
-      <c r="C24">
-        <v>0.9</v>
-      </c>
-      <c r="D24">
-        <v>0.95</v>
-      </c>
-      <c r="J24">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B25">
-        <v>0.8</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>0.1</v>
-      </c>
-      <c r="D27">
-        <v>0.8</v>
-      </c>
-      <c r="J27">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
-        <v>0.2</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="J28">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29">
-        <v>0.3</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="J29">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30">
-        <v>0.4</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="J30">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31">
-        <v>0.5</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="J31">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32">
-        <v>0.6</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="J32">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33">
-        <v>0.7</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="J33">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34">
-        <v>0.8</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="J34">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35">
-        <v>0.9</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="J35">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
-      </c>
-      <c r="J36">
+      <c r="J137">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="138" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="E138">
+        <v>1</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
         <v>1</v>
       </c>
     </row>

--- a/src/components/LugCalculator/Kn.xlsx
+++ b/src/components/LugCalculator/Kn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\portfolio\src\components\LugCalculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBDB3BA9-FB0A-440A-B01D-A26CEC15CA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732969A9-EAE0-48C8-B575-BB8EBE62505E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B86692AA-6AD1-4F17-95A9-760893952109}"/>
   </bookViews>
@@ -7158,10 +7158,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DED8BC0-7630-4FEC-A3D6-F44AF91D8DCF}">
-  <dimension ref="B2:M138"/>
+  <dimension ref="B2:M141"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="10" width="13.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="13.109375" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.3">
@@ -9027,7 +9029,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65" s="1">
         <v>1</v>
       </c>
@@ -9056,7 +9058,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B66" s="1">
         <v>1</v>
       </c>
@@ -9085,13 +9087,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B70" t="str">
         <f>_xlfn.CONCAT(B$3,": ",B4,", ")</f>
         <v xml:space="preserve">Fty_Ftu: 0.6, </v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>0</v>
       </c>
@@ -9120,1836 +9122,2662 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B76">
-        <v>0.6</v>
-      </c>
-      <c r="C76">
-        <v>0</v>
-      </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76">
-        <v>0</v>
-      </c>
-      <c r="G76">
-        <v>0</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B77">
-        <v>0.6</v>
-      </c>
-      <c r="C77">
-        <v>0.05</v>
-      </c>
-      <c r="D77">
-        <v>0.33</v>
-      </c>
-      <c r="E77">
-        <v>0.33</v>
-      </c>
-      <c r="F77">
-        <v>0.26</v>
-      </c>
-      <c r="G77">
-        <v>0.15</v>
-      </c>
-      <c r="H77">
-        <v>0.09</v>
-      </c>
-      <c r="I77">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="J77">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B78">
-        <v>0.6</v>
-      </c>
-      <c r="C78">
-        <v>0.1</v>
-      </c>
-      <c r="D78">
-        <v>0.5</v>
-      </c>
-      <c r="E78">
-        <v>0.49</v>
-      </c>
-      <c r="F78">
-        <v>0.41</v>
-      </c>
-      <c r="G78">
-        <v>0.24</v>
-      </c>
-      <c r="H78">
-        <v>0.16</v>
-      </c>
-      <c r="I78">
-        <v>0.12</v>
-      </c>
-      <c r="J78">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B79">
-        <v>0.6</v>
-      </c>
-      <c r="C79">
-        <v>0.15</v>
-      </c>
-      <c r="D79">
-        <v>0.61</v>
-      </c>
-      <c r="E79">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="F79">
-        <v>0.52</v>
-      </c>
-      <c r="G79">
-        <v>0.32</v>
-      </c>
-      <c r="H79">
-        <v>0.22</v>
-      </c>
-      <c r="I79">
-        <v>0.18</v>
-      </c>
-      <c r="J79">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B80">
-        <v>0.6</v>
-      </c>
-      <c r="C80">
-        <v>0.2</v>
-      </c>
-      <c r="D80">
-        <v>0.67</v>
-      </c>
-      <c r="E80">
-        <v>0.65</v>
-      </c>
-      <c r="F80">
-        <v>0.59</v>
-      </c>
-      <c r="G80">
-        <v>0.4</v>
-      </c>
-      <c r="H80">
-        <v>0.3</v>
-      </c>
-      <c r="I80">
-        <v>0.24</v>
-      </c>
-      <c r="J80">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B81">
-        <v>0.6</v>
-      </c>
-      <c r="C81">
-        <v>0.25</v>
-      </c>
-      <c r="D81">
-        <v>0.7</v>
-      </c>
-      <c r="E81">
-        <v>0.68</v>
-      </c>
-      <c r="F81">
-        <v>0.63</v>
-      </c>
-      <c r="G81">
-        <v>0.47</v>
-      </c>
-      <c r="H81">
-        <v>0.36</v>
-      </c>
-      <c r="I81">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="J81">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B82">
-        <v>0.6</v>
-      </c>
-      <c r="C82">
-        <v>0.3</v>
-      </c>
-      <c r="D82">
-        <v>0.71</v>
-      </c>
-      <c r="E82">
-        <v>0.69</v>
-      </c>
-      <c r="F82">
-        <v>0.66</v>
-      </c>
-      <c r="G82">
-        <v>0.53</v>
-      </c>
-      <c r="H82">
-        <v>0.41</v>
-      </c>
-      <c r="I82">
-        <v>0.33</v>
-      </c>
-      <c r="J82">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B83">
-        <v>0.6</v>
-      </c>
-      <c r="C83">
-        <v>0.35</v>
-      </c>
-      <c r="D83">
-        <v>0.72</v>
-      </c>
-      <c r="E83">
-        <v>0.7</v>
-      </c>
-      <c r="F83">
-        <v>0.68</v>
-      </c>
-      <c r="G83">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="H83">
-        <v>0.45</v>
-      </c>
-      <c r="I83">
-        <v>0.37</v>
-      </c>
-      <c r="J83">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B84">
-        <v>0.6</v>
-      </c>
-      <c r="C84">
-        <v>0.4</v>
-      </c>
-      <c r="D84">
-        <v>0.73</v>
-      </c>
-      <c r="E84">
-        <v>0.71</v>
-      </c>
-      <c r="F84">
-        <v>0.69</v>
-      </c>
-      <c r="G84">
-        <v>0.61</v>
-      </c>
-      <c r="H84">
-        <v>0.49</v>
-      </c>
-      <c r="I84">
-        <v>0.4</v>
-      </c>
-      <c r="J84">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B85">
-        <v>0.6</v>
-      </c>
-      <c r="C85">
-        <v>0.45</v>
-      </c>
-      <c r="D85">
-        <v>0.74</v>
-      </c>
-      <c r="E85">
-        <v>0.72</v>
-      </c>
-      <c r="F85">
-        <v>0.7</v>
-      </c>
-      <c r="G85">
-        <v>0.63</v>
-      </c>
-      <c r="H85">
-        <v>0.53</v>
-      </c>
-      <c r="I85">
-        <v>0.43</v>
-      </c>
-      <c r="J85">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B86">
-        <v>0.6</v>
-      </c>
-      <c r="C86">
-        <v>0.5</v>
-      </c>
-      <c r="D86">
-        <v>0.76</v>
-      </c>
-      <c r="E86">
-        <v>0.74</v>
-      </c>
-      <c r="F86">
-        <v>0.72</v>
-      </c>
-      <c r="G86">
-        <v>0.64</v>
-      </c>
-      <c r="H86">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="I86">
-        <v>0.46</v>
-      </c>
-      <c r="J86">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B87">
-        <v>0.6</v>
-      </c>
-      <c r="C87">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D87">
-        <v>0.77</v>
-      </c>
-      <c r="E87">
-        <v>0.76</v>
-      </c>
-      <c r="F87">
-        <v>0.73</v>
-      </c>
-      <c r="G87">
-        <v>0.66</v>
-      </c>
-      <c r="H87">
-        <v>0.59</v>
-      </c>
-      <c r="I87">
-        <v>0.5</v>
-      </c>
-      <c r="J87">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B88">
-        <v>0.6</v>
-      </c>
-      <c r="C88">
-        <v>0.6</v>
-      </c>
-      <c r="D88">
-        <v>0.78</v>
-      </c>
-      <c r="E88">
-        <v>0.77</v>
-      </c>
-      <c r="F88">
-        <v>0.74</v>
-      </c>
-      <c r="G88">
-        <v>0.68</v>
-      </c>
-      <c r="H88">
-        <v>0.62</v>
-      </c>
-      <c r="I88">
-        <v>0.53</v>
-      </c>
-      <c r="J88">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B89">
-        <v>0.6</v>
-      </c>
-      <c r="C89">
-        <v>0.65</v>
-      </c>
-      <c r="D89">
-        <v>0.8</v>
-      </c>
-      <c r="E89">
-        <v>0.79</v>
-      </c>
-      <c r="F89">
-        <v>0.77</v>
-      </c>
-      <c r="G89">
-        <v>0.7</v>
-      </c>
-      <c r="H89">
-        <v>0.64</v>
-      </c>
-      <c r="I89">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="J89">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B90">
-        <v>0.6</v>
-      </c>
-      <c r="C90">
-        <v>0.7</v>
-      </c>
-      <c r="D90">
-        <v>0.82</v>
-      </c>
-      <c r="E90">
-        <v>0.81</v>
-      </c>
-      <c r="F90">
-        <v>0.78</v>
-      </c>
-      <c r="G90">
-        <v>0.73</v>
-      </c>
-      <c r="H90">
-        <v>0.68</v>
-      </c>
-      <c r="I90">
-        <v>0.61</v>
-      </c>
-      <c r="J90">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B91">
-        <v>0.6</v>
-      </c>
-      <c r="C91">
-        <v>0.75</v>
-      </c>
-      <c r="D91">
-        <v>0.84</v>
-      </c>
-      <c r="E91">
-        <v>0.82</v>
-      </c>
-      <c r="F91">
-        <v>0.81</v>
-      </c>
-      <c r="G91">
-        <v>0.77</v>
-      </c>
-      <c r="H91">
-        <v>0.72</v>
-      </c>
-      <c r="I91">
-        <v>0.66</v>
-      </c>
-      <c r="J91">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B92">
-        <v>0.6</v>
-      </c>
-      <c r="C92">
-        <v>0.8</v>
-      </c>
-      <c r="D92">
-        <v>0.86</v>
-      </c>
-      <c r="E92">
-        <v>0.84</v>
-      </c>
-      <c r="F92">
-        <v>0.84</v>
-      </c>
-      <c r="G92">
-        <v>0.8</v>
-      </c>
-      <c r="H92">
-        <v>0.76</v>
-      </c>
-      <c r="I92">
-        <v>0.71</v>
-      </c>
-      <c r="J92">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B93">
-        <v>0.6</v>
-      </c>
-      <c r="C93">
-        <v>0.85</v>
-      </c>
-      <c r="D93">
-        <v>0.88</v>
-      </c>
-      <c r="E93">
-        <v>0.87</v>
-      </c>
-      <c r="F93">
-        <v>0.87</v>
-      </c>
-      <c r="G93">
-        <v>0.84</v>
-      </c>
-      <c r="H93">
-        <v>0.81</v>
-      </c>
-      <c r="I93">
-        <v>0.77</v>
-      </c>
-      <c r="J93">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B94">
-        <v>0.6</v>
-      </c>
-      <c r="C94">
-        <v>0.9</v>
-      </c>
-      <c r="D94">
-        <v>0.91</v>
-      </c>
-      <c r="E94">
-        <v>0.9</v>
-      </c>
-      <c r="F94">
-        <v>0.9</v>
-      </c>
-      <c r="G94">
-        <v>0.88</v>
-      </c>
-      <c r="H94">
-        <v>0.86</v>
-      </c>
-      <c r="I94">
-        <v>0.83</v>
-      </c>
-      <c r="J94">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B95">
-        <v>0.6</v>
-      </c>
-      <c r="C95">
-        <v>0.95</v>
-      </c>
-      <c r="D95">
-        <v>0.95</v>
-      </c>
-      <c r="E95">
-        <v>0.95</v>
-      </c>
-      <c r="F95">
-        <v>0.95</v>
-      </c>
-      <c r="G95">
-        <v>0.94</v>
-      </c>
-      <c r="H95">
-        <v>0.94</v>
-      </c>
-      <c r="I95">
-        <v>0.92</v>
-      </c>
-      <c r="J95">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B96">
-        <v>0.6</v>
-      </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-      <c r="D96">
-        <v>1</v>
-      </c>
-      <c r="E96">
-        <v>1</v>
-      </c>
-      <c r="F96">
-        <v>1</v>
-      </c>
-      <c r="G96">
-        <v>1</v>
-      </c>
-      <c r="H96">
-        <v>1</v>
-      </c>
-      <c r="I96">
-        <v>1</v>
-      </c>
-      <c r="J96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B97">
-        <v>0.8</v>
-      </c>
-      <c r="C97">
-        <v>0</v>
-      </c>
-      <c r="D97">
-        <v>0</v>
-      </c>
-      <c r="E97">
-        <v>0</v>
-      </c>
-      <c r="F97">
-        <v>0</v>
-      </c>
-      <c r="G97">
-        <v>0</v>
-      </c>
-      <c r="H97">
-        <v>0</v>
-      </c>
-      <c r="I97">
-        <v>0</v>
-      </c>
-      <c r="J97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B98">
-        <v>0.8</v>
-      </c>
-      <c r="C98">
-        <v>0.05</v>
-      </c>
-      <c r="D98">
-        <v>0.4</v>
-      </c>
-      <c r="E98">
-        <v>0.38</v>
-      </c>
-      <c r="F98">
-        <v>0.24</v>
-      </c>
-      <c r="G98">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="H98">
-        <v>0.08</v>
-      </c>
-      <c r="I98">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="J98">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B99">
-        <v>0.8</v>
-      </c>
-      <c r="C99">
-        <v>0.1</v>
-      </c>
-      <c r="D99">
-        <v>0.66</v>
-      </c>
-      <c r="E99">
-        <v>0.59</v>
-      </c>
-      <c r="F99">
-        <v>0.42</v>
-      </c>
-      <c r="G99">
-        <v>0.25</v>
-      </c>
-      <c r="H99">
-        <v>0.15</v>
-      </c>
-      <c r="I99">
-        <v>0.12</v>
-      </c>
-      <c r="J99">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B100">
-        <v>0.8</v>
-      </c>
-      <c r="C100">
-        <v>0.15</v>
-      </c>
-      <c r="D100">
-        <v>0.79</v>
-      </c>
-      <c r="E100">
-        <v>0.73</v>
-      </c>
-      <c r="F100">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="G100">
-        <v>0.35</v>
-      </c>
-      <c r="H100">
-        <v>0.22</v>
-      </c>
-      <c r="I100">
-        <v>0.18</v>
-      </c>
-      <c r="J100">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101">
-        <v>0.8</v>
-      </c>
-      <c r="C101">
-        <v>0.2</v>
-      </c>
-      <c r="D101">
-        <v>0.83</v>
-      </c>
-      <c r="E101">
-        <v>0.81</v>
-      </c>
-      <c r="F101">
-        <v>0.67</v>
-      </c>
-      <c r="G101">
-        <v>0.43</v>
-      </c>
-      <c r="H101">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="I101">
-        <v>0.23</v>
-      </c>
-      <c r="J101">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B102">
-        <v>0.8</v>
-      </c>
-      <c r="C102">
-        <v>0.25</v>
-      </c>
-      <c r="D102">
-        <v>0.84</v>
-      </c>
-      <c r="E102">
-        <v>0.83</v>
-      </c>
-      <c r="F102">
-        <v>0.74</v>
-      </c>
-      <c r="G102">
-        <v>0.5</v>
-      </c>
-      <c r="H102">
-        <v>0.36</v>
-      </c>
-      <c r="I102">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="J102">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B103">
-        <v>0.8</v>
-      </c>
-      <c r="C103">
-        <v>0.3</v>
-      </c>
-      <c r="D103">
-        <v>0.85</v>
-      </c>
-      <c r="E103">
-        <v>0.84</v>
-      </c>
-      <c r="F103">
-        <v>0.77</v>
-      </c>
-      <c r="G103">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H103">
-        <v>0.42</v>
-      </c>
-      <c r="I103">
-        <v>0.33</v>
-      </c>
-      <c r="J103">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B104">
-        <v>0.8</v>
-      </c>
-      <c r="C104">
-        <v>0.35</v>
-      </c>
-      <c r="D104">
-        <v>0.85</v>
-      </c>
-      <c r="E104">
-        <v>0.85</v>
-      </c>
-      <c r="F104">
-        <v>0.8</v>
-      </c>
-      <c r="G104">
-        <v>0.62</v>
-      </c>
-      <c r="H104">
-        <v>0.48</v>
-      </c>
-      <c r="I104">
-        <v>0.37</v>
-      </c>
-      <c r="J104">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B105">
-        <v>0.8</v>
-      </c>
-      <c r="C105">
-        <v>0.4</v>
-      </c>
-      <c r="D105">
-        <v>0.86</v>
-      </c>
-      <c r="E105">
-        <v>0.86</v>
-      </c>
-      <c r="F105">
-        <v>0.81</v>
-      </c>
-      <c r="G105">
-        <v>0.66</v>
-      </c>
-      <c r="H105">
-        <v>0.52</v>
-      </c>
-      <c r="I105">
-        <v>0.41</v>
-      </c>
-      <c r="J105">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B106">
-        <v>0.8</v>
-      </c>
-      <c r="C106">
-        <v>0.45</v>
-      </c>
-      <c r="D106">
-        <v>0.86</v>
-      </c>
-      <c r="E106">
-        <v>0.86</v>
-      </c>
-      <c r="F106">
-        <v>0.83</v>
-      </c>
-      <c r="G106">
-        <v>0.69</v>
-      </c>
-      <c r="H106">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="I106">
-        <v>0.44</v>
-      </c>
-      <c r="J106">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B107">
-        <v>0.8</v>
-      </c>
-      <c r="C107">
-        <v>0.5</v>
-      </c>
-      <c r="D107">
-        <v>0.87</v>
-      </c>
-      <c r="E107">
-        <v>0.87</v>
-      </c>
-      <c r="F107">
-        <v>0.84</v>
-      </c>
-      <c r="G107">
-        <v>0.72</v>
-      </c>
-      <c r="H107">
-        <v>0.59</v>
-      </c>
-      <c r="I107">
-        <v>0.47</v>
-      </c>
-      <c r="J107">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B108">
-        <v>0.8</v>
-      </c>
-      <c r="C108">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D108">
-        <v>0.88</v>
-      </c>
-      <c r="E108">
-        <v>0.88</v>
-      </c>
-      <c r="F108">
-        <v>0.84</v>
-      </c>
-      <c r="G108">
-        <v>0.74</v>
-      </c>
-      <c r="H108">
-        <v>0.62</v>
-      </c>
-      <c r="I108">
-        <v>0.51</v>
-      </c>
-      <c r="J108">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B109">
-        <v>0.8</v>
-      </c>
-      <c r="C109">
-        <v>0.6</v>
-      </c>
-      <c r="D109">
-        <v>0.89</v>
-      </c>
-      <c r="E109">
-        <v>0.89</v>
-      </c>
-      <c r="F109">
-        <v>0.85</v>
-      </c>
-      <c r="G109">
-        <v>0.76</v>
-      </c>
-      <c r="H109">
-        <v>0.65</v>
-      </c>
-      <c r="I109">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J109">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B110">
-        <v>0.8</v>
-      </c>
-      <c r="C110">
-        <v>0.65</v>
-      </c>
-      <c r="D110">
-        <v>0.9</v>
-      </c>
-      <c r="E110">
-        <v>0.9</v>
-      </c>
-      <c r="F110">
-        <v>0.86</v>
-      </c>
-      <c r="G110">
-        <v>0.79</v>
-      </c>
-      <c r="H110">
-        <v>0.68</v>
-      </c>
-      <c r="I110">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="J110">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B111">
-        <v>0.8</v>
-      </c>
-      <c r="C111">
-        <v>0.7</v>
-      </c>
-      <c r="D111">
-        <v>0.9</v>
-      </c>
-      <c r="E111">
-        <v>0.9</v>
-      </c>
-      <c r="F111">
-        <v>0.87</v>
-      </c>
-      <c r="G111">
-        <v>0.82</v>
-      </c>
-      <c r="H111">
-        <v>0.72</v>
-      </c>
-      <c r="I111">
-        <v>0.63</v>
-      </c>
-      <c r="J111">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B112">
-        <v>0.8</v>
-      </c>
-      <c r="C112">
-        <v>0.75</v>
-      </c>
-      <c r="D112">
-        <v>0.91</v>
-      </c>
-      <c r="E112">
-        <v>0.91</v>
-      </c>
-      <c r="F112">
-        <v>0.89</v>
-      </c>
-      <c r="G112">
-        <v>0.84</v>
-      </c>
-      <c r="H112">
-        <v>0.77</v>
-      </c>
-      <c r="I112">
-        <v>0.69</v>
-      </c>
-      <c r="J112">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B113">
-        <v>0.8</v>
-      </c>
-      <c r="C113">
-        <v>0.8</v>
-      </c>
-      <c r="D113">
-        <v>0.92</v>
-      </c>
-      <c r="E113">
-        <v>0.92</v>
-      </c>
-      <c r="F113">
-        <v>0.92</v>
-      </c>
-      <c r="G113">
-        <v>0.88</v>
-      </c>
-      <c r="H113">
-        <v>0.83</v>
-      </c>
-      <c r="I113">
-        <v>0.74</v>
-      </c>
-      <c r="J113">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B114">
-        <v>0.8</v>
-      </c>
-      <c r="C114">
-        <v>0.85</v>
-      </c>
-      <c r="D114">
-        <v>0.94</v>
-      </c>
-      <c r="E114">
-        <v>0.94</v>
-      </c>
-      <c r="F114">
-        <v>0.94</v>
-      </c>
-      <c r="G114">
-        <v>0.91</v>
-      </c>
-      <c r="H114">
-        <v>0.87</v>
-      </c>
-      <c r="I114">
-        <v>0.79</v>
-      </c>
-      <c r="J114">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B115">
-        <v>0.8</v>
-      </c>
-      <c r="C115">
-        <v>0.9</v>
-      </c>
-      <c r="D115">
-        <v>0.96</v>
-      </c>
-      <c r="E115">
-        <v>0.96</v>
-      </c>
-      <c r="F115">
-        <v>0.96</v>
-      </c>
-      <c r="G115">
-        <v>0.94</v>
-      </c>
-      <c r="H115">
-        <v>0.91</v>
-      </c>
-      <c r="I115">
-        <v>0.85</v>
-      </c>
-      <c r="J115">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B116">
-        <v>0.8</v>
-      </c>
-      <c r="C116">
-        <v>0.95</v>
-      </c>
-      <c r="D116">
-        <v>0.97</v>
-      </c>
-      <c r="E116">
-        <v>0.97</v>
-      </c>
-      <c r="F116">
-        <v>0.97</v>
-      </c>
-      <c r="G116">
-        <v>0.97</v>
-      </c>
-      <c r="H116">
-        <v>0.95</v>
-      </c>
-      <c r="I116">
-        <v>0.92</v>
-      </c>
-      <c r="J116">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B117">
-        <v>0.8</v>
-      </c>
-      <c r="C117">
-        <v>1</v>
-      </c>
-      <c r="D117">
-        <v>1</v>
-      </c>
-      <c r="E117">
-        <v>1</v>
-      </c>
-      <c r="F117">
-        <v>1</v>
-      </c>
-      <c r="G117">
-        <v>1</v>
-      </c>
-      <c r="H117">
-        <v>1</v>
-      </c>
-      <c r="I117">
-        <v>1</v>
-      </c>
-      <c r="J117">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B118">
-        <v>1</v>
-      </c>
-      <c r="C118">
-        <v>0</v>
-      </c>
-      <c r="D118">
-        <v>0</v>
-      </c>
-      <c r="E118">
-        <v>0</v>
-      </c>
-      <c r="F118">
-        <v>0</v>
-      </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B119">
-        <v>1</v>
-      </c>
-      <c r="C119">
-        <v>0.05</v>
-      </c>
-      <c r="D119">
-        <v>0.54</v>
-      </c>
-      <c r="E119">
-        <v>0.44</v>
-      </c>
-      <c r="F119">
-        <v>0.26</v>
-      </c>
-      <c r="G119">
-        <v>0.13</v>
-      </c>
-      <c r="H119">
-        <v>0.09</v>
-      </c>
-      <c r="I119">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="J119">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B120">
-        <v>1</v>
-      </c>
-      <c r="C120">
-        <v>0.1</v>
-      </c>
-      <c r="D120">
-        <v>0.78</v>
-      </c>
-      <c r="E120">
-        <v>0.69</v>
-      </c>
-      <c r="F120">
-        <v>0.44</v>
-      </c>
-      <c r="G120">
-        <v>0.22</v>
-      </c>
-      <c r="H120">
-        <v>0.16</v>
-      </c>
-      <c r="I120">
-        <v>0.13</v>
-      </c>
-      <c r="J120">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B121">
-        <v>1</v>
-      </c>
-      <c r="C121">
-        <v>0.15</v>
-      </c>
-      <c r="D121">
-        <v>0.93</v>
-      </c>
-      <c r="E121">
-        <v>0.86</v>
-      </c>
-      <c r="F121">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="G121">
-        <v>0.31</v>
-      </c>
-      <c r="H121">
-        <v>0.23</v>
-      </c>
-      <c r="I121">
-        <v>0.18</v>
-      </c>
-      <c r="J121">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B122">
-        <v>1</v>
-      </c>
-      <c r="C122">
-        <v>0.2</v>
-      </c>
-      <c r="D122">
-        <v>1</v>
-      </c>
-      <c r="E122">
-        <v>0.96</v>
-      </c>
-      <c r="F122">
-        <v>0.71</v>
-      </c>
-      <c r="G122">
-        <v>0.42</v>
-      </c>
-      <c r="H122">
-        <v>0.3</v>
-      </c>
-      <c r="I122">
-        <v>0.23</v>
-      </c>
-      <c r="J122">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B123">
-        <v>1</v>
-      </c>
-      <c r="C123">
-        <v>0.25</v>
-      </c>
-      <c r="D123">
-        <v>1</v>
-      </c>
-      <c r="E123">
-        <v>0.98</v>
-      </c>
-      <c r="F123">
-        <v>0.8</v>
-      </c>
-      <c r="G123">
-        <v>0.5</v>
-      </c>
-      <c r="H123">
-        <v>0.36</v>
-      </c>
-      <c r="I123">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="J123">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B124">
-        <v>1</v>
-      </c>
-      <c r="C124">
-        <v>0.3</v>
-      </c>
-      <c r="D124">
-        <v>1</v>
-      </c>
-      <c r="E124">
-        <v>0.99</v>
-      </c>
-      <c r="F124">
-        <v>0.87</v>
-      </c>
-      <c r="G124">
-        <v>0.6</v>
-      </c>
-      <c r="H124">
-        <v>0.42</v>
-      </c>
-      <c r="I124">
-        <v>0.33</v>
-      </c>
-      <c r="J124">
-        <v>0.28000000000000003</v>
-      </c>
-    </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B125">
-        <v>1</v>
-      </c>
-      <c r="C125">
-        <v>0.35</v>
-      </c>
-      <c r="D125">
-        <v>1</v>
-      </c>
-      <c r="E125">
-        <v>0.99</v>
-      </c>
-      <c r="F125">
-        <v>0.93</v>
-      </c>
-      <c r="G125">
-        <v>0.66</v>
-      </c>
-      <c r="H125">
-        <v>0.48</v>
-      </c>
-      <c r="I125">
-        <v>0.37</v>
-      </c>
-      <c r="J125">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B126">
-        <v>1</v>
-      </c>
-      <c r="C126">
-        <v>0.4</v>
-      </c>
-      <c r="D126">
-        <v>1</v>
-      </c>
-      <c r="E126">
-        <v>1</v>
-      </c>
-      <c r="F126">
-        <v>0.96</v>
-      </c>
-      <c r="G126">
-        <v>0.71</v>
-      </c>
-      <c r="H126">
-        <v>0.53</v>
-      </c>
-      <c r="I126">
-        <v>0.41</v>
-      </c>
-      <c r="J126">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B127">
-        <v>1</v>
-      </c>
-      <c r="C127">
-        <v>0.45</v>
-      </c>
-      <c r="D127">
-        <v>1</v>
-      </c>
-      <c r="E127">
-        <v>1</v>
-      </c>
-      <c r="F127">
-        <v>0.97</v>
-      </c>
-      <c r="G127">
-        <v>0.75</v>
-      </c>
-      <c r="H127">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="I127">
-        <v>0.45</v>
-      </c>
-      <c r="J127">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B128">
-        <v>1</v>
-      </c>
-      <c r="C128">
-        <v>0.5</v>
-      </c>
-      <c r="D128">
-        <v>1</v>
-      </c>
-      <c r="E128">
-        <v>1</v>
-      </c>
-      <c r="F128">
-        <v>0.96</v>
-      </c>
-      <c r="G128">
-        <v>0.78</v>
-      </c>
-      <c r="H128">
-        <v>0.62</v>
-      </c>
-      <c r="I128">
-        <v>0.49</v>
-      </c>
-      <c r="J128">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B129">
-        <v>1</v>
-      </c>
-      <c r="C129">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D129">
-        <v>1</v>
-      </c>
-      <c r="E129">
-        <v>1</v>
-      </c>
-      <c r="F129">
-        <v>0.96</v>
-      </c>
-      <c r="G129">
-        <v>0.8</v>
-      </c>
-      <c r="H129">
-        <v>0.66</v>
-      </c>
-      <c r="I129">
-        <v>0.53</v>
-      </c>
-      <c r="J129">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B130">
-        <v>1</v>
-      </c>
-      <c r="C130">
-        <v>0.6</v>
-      </c>
-      <c r="D130">
-        <v>1</v>
-      </c>
-      <c r="E130">
-        <v>1</v>
-      </c>
-      <c r="F130">
-        <v>0.96</v>
-      </c>
-      <c r="G130">
-        <v>0.83</v>
-      </c>
-      <c r="H130">
-        <v>0.69</v>
-      </c>
-      <c r="I130">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="J130">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B131">
-        <v>1</v>
-      </c>
-      <c r="C131">
-        <v>0.65</v>
-      </c>
-      <c r="D131">
-        <v>1</v>
-      </c>
-      <c r="E131">
-        <v>1</v>
-      </c>
-      <c r="F131">
-        <v>0.96</v>
-      </c>
-      <c r="G131">
-        <v>0.87</v>
-      </c>
-      <c r="H131">
-        <v>0.73</v>
-      </c>
-      <c r="I131">
-        <v>0.6</v>
-      </c>
-      <c r="J131">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B132">
-        <v>1</v>
-      </c>
-      <c r="C132">
-        <v>0.7</v>
-      </c>
-      <c r="D132">
-        <v>1</v>
-      </c>
-      <c r="E132">
-        <v>1</v>
-      </c>
-      <c r="F132">
-        <v>0.97</v>
-      </c>
-      <c r="G132">
-        <v>0.9</v>
-      </c>
-      <c r="H132">
-        <v>0.78</v>
-      </c>
-      <c r="I132">
-        <v>0.64</v>
-      </c>
-      <c r="J132">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B133">
-        <v>1</v>
-      </c>
-      <c r="C133">
-        <v>0.75</v>
-      </c>
-      <c r="D133">
-        <v>1</v>
-      </c>
-      <c r="E133">
-        <v>1</v>
-      </c>
-      <c r="F133">
-        <v>0.99</v>
-      </c>
-      <c r="G133">
-        <v>0.93</v>
-      </c>
-      <c r="H133">
-        <v>0.84</v>
-      </c>
-      <c r="I133">
-        <v>0.7</v>
-      </c>
-      <c r="J133">
-        <v>0.56999999999999995</v>
-      </c>
-    </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B134">
-        <v>1</v>
-      </c>
-      <c r="C134">
-        <v>0.8</v>
-      </c>
-      <c r="D134">
-        <v>1</v>
-      </c>
-      <c r="E134">
-        <v>1</v>
-      </c>
-      <c r="F134">
-        <v>1</v>
-      </c>
-      <c r="G134">
-        <v>0.97</v>
-      </c>
-      <c r="H134">
-        <v>0.91</v>
-      </c>
-      <c r="I134">
-        <v>0.76</v>
-      </c>
-      <c r="J134">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B135">
-        <v>1</v>
-      </c>
-      <c r="C135">
-        <v>0.85</v>
-      </c>
-      <c r="D135">
-        <v>1</v>
-      </c>
-      <c r="E135">
-        <v>1</v>
-      </c>
-      <c r="F135">
-        <v>0.99</v>
-      </c>
-      <c r="G135">
-        <v>0.99</v>
-      </c>
-      <c r="H135">
-        <v>0.94</v>
-      </c>
-      <c r="I135">
-        <v>0.81</v>
-      </c>
-      <c r="J135">
-        <v>0.69</v>
-      </c>
-    </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B136">
-        <v>1</v>
-      </c>
-      <c r="C136">
-        <v>0.9</v>
-      </c>
-      <c r="D136">
-        <v>1</v>
-      </c>
-      <c r="E136">
-        <v>1</v>
-      </c>
-      <c r="F136">
-        <v>1</v>
-      </c>
-      <c r="G136">
-        <v>1</v>
-      </c>
-      <c r="H136">
-        <v>0.97</v>
-      </c>
-      <c r="I136">
-        <v>0.86</v>
-      </c>
-      <c r="J136">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B137">
-        <v>1</v>
-      </c>
-      <c r="C137">
-        <v>0.95</v>
-      </c>
-      <c r="D137">
-        <v>1</v>
-      </c>
-      <c r="E137">
-        <v>1</v>
-      </c>
-      <c r="F137">
-        <v>1</v>
-      </c>
-      <c r="G137">
-        <v>1</v>
-      </c>
-      <c r="H137">
-        <v>0.99</v>
-      </c>
-      <c r="I137">
-        <v>0.92</v>
-      </c>
-      <c r="J137">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B138">
-        <v>1</v>
-      </c>
-      <c r="C138">
-        <v>1</v>
-      </c>
-      <c r="D138">
-        <v>1</v>
-      </c>
-      <c r="E138">
-        <v>1</v>
-      </c>
-      <c r="F138">
-        <v>1</v>
-      </c>
-      <c r="G138">
-        <v>1</v>
-      </c>
-      <c r="H138">
-        <v>1</v>
-      </c>
-      <c r="I138">
-        <v>1</v>
-      </c>
-      <c r="J138">
-        <v>1</v>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B76" t="str">
+        <f>_xlfn.CONCAT("{",B$75,": ",B4, ", ")</f>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C76" t="str">
+        <f t="shared" ref="C76:J76" si="0">_xlfn.CONCAT(C$75,": ",C4, ", ")</f>
+        <v xml:space="preserve">Dw: 0, </v>
+      </c>
+      <c r="D76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0, </v>
+      </c>
+      <c r="E76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0, </v>
+      </c>
+      <c r="F76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0, </v>
+      </c>
+      <c r="G76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0, </v>
+      </c>
+      <c r="H76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0, </v>
+      </c>
+      <c r="I76" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0, </v>
+      </c>
+      <c r="J76" t="str">
+        <f>_xlfn.CONCAT(J$75,": ",J4, "}, ")</f>
+        <v xml:space="preserve">Fty_E_eu_10: 0}, </v>
+      </c>
+      <c r="L76" t="str">
+        <f>_xlfn.CONCAT(B76:J76)</f>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0, Fty_E_eu_0: 0, Fty_E_eu_1: 0, Fty_E_eu_2: 0, Fty_E_eu_4: 0, Fty_E_eu_6: 0, Fty_E_eu_8: 0, Fty_E_eu_10: 0}, </v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B77" t="str">
+        <f t="shared" ref="B77:B138" si="1">_xlfn.CONCAT("{",B$75,": ",B5, ", ")</f>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C77" t="str">
+        <f t="shared" ref="B77:J77" si="2">_xlfn.CONCAT(C$75,": ",C5, ", ")</f>
+        <v xml:space="preserve">Dw: 0.05, </v>
+      </c>
+      <c r="D77" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.33, </v>
+      </c>
+      <c r="E77" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.33, </v>
+      </c>
+      <c r="F77" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.26, </v>
+      </c>
+      <c r="G77" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.15, </v>
+      </c>
+      <c r="H77" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.09, </v>
+      </c>
+      <c r="I77" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.07, </v>
+      </c>
+      <c r="J77" t="str">
+        <f t="shared" ref="J77:J138" si="3">_xlfn.CONCAT(J$75,": ",J5, "}, ")</f>
+        <v xml:space="preserve">Fty_E_eu_10: 0.06}, </v>
+      </c>
+      <c r="L77" t="str">
+        <f t="shared" ref="L77:L138" si="4">_xlfn.CONCAT(B77:J77)</f>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.05, Fty_E_eu_0: 0.33, Fty_E_eu_1: 0.33, Fty_E_eu_2: 0.26, Fty_E_eu_4: 0.15, Fty_E_eu_6: 0.09, Fty_E_eu_8: 0.07, Fty_E_eu_10: 0.06}, </v>
+      </c>
+    </row>
+    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B78" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C78" t="str">
+        <f t="shared" ref="B78:J78" si="5">_xlfn.CONCAT(C$75,": ",C6, ", ")</f>
+        <v xml:space="preserve">Dw: 0.1, </v>
+      </c>
+      <c r="D78" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.5, </v>
+      </c>
+      <c r="E78" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.49, </v>
+      </c>
+      <c r="F78" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.41, </v>
+      </c>
+      <c r="G78" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.24, </v>
+      </c>
+      <c r="H78" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.16, </v>
+      </c>
+      <c r="I78" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.12, </v>
+      </c>
+      <c r="J78" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.1}, </v>
+      </c>
+      <c r="L78" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.1, Fty_E_eu_0: 0.5, Fty_E_eu_1: 0.49, Fty_E_eu_2: 0.41, Fty_E_eu_4: 0.24, Fty_E_eu_6: 0.16, Fty_E_eu_8: 0.12, Fty_E_eu_10: 0.1}, </v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B79" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C79" t="str">
+        <f t="shared" ref="B79:J79" si="6">_xlfn.CONCAT(C$75,": ",C7, ", ")</f>
+        <v xml:space="preserve">Dw: 0.15, </v>
+      </c>
+      <c r="D79" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.61, </v>
+      </c>
+      <c r="E79" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.58, </v>
+      </c>
+      <c r="F79" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.52, </v>
+      </c>
+      <c r="G79" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.32, </v>
+      </c>
+      <c r="H79" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.22, </v>
+      </c>
+      <c r="I79" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.18, </v>
+      </c>
+      <c r="J79" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.15}, </v>
+      </c>
+      <c r="L79" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.15, Fty_E_eu_0: 0.61, Fty_E_eu_1: 0.58, Fty_E_eu_2: 0.52, Fty_E_eu_4: 0.32, Fty_E_eu_6: 0.22, Fty_E_eu_8: 0.18, Fty_E_eu_10: 0.15}, </v>
+      </c>
+    </row>
+    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B80" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C80" t="str">
+        <f t="shared" ref="B80:J80" si="7">_xlfn.CONCAT(C$75,": ",C8, ", ")</f>
+        <v xml:space="preserve">Dw: 0.2, </v>
+      </c>
+      <c r="D80" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.67, </v>
+      </c>
+      <c r="E80" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.65, </v>
+      </c>
+      <c r="F80" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.59, </v>
+      </c>
+      <c r="G80" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.4, </v>
+      </c>
+      <c r="H80" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.3, </v>
+      </c>
+      <c r="I80" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.24, </v>
+      </c>
+      <c r="J80" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.19}, </v>
+      </c>
+      <c r="L80" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.2, Fty_E_eu_0: 0.67, Fty_E_eu_1: 0.65, Fty_E_eu_2: 0.59, Fty_E_eu_4: 0.4, Fty_E_eu_6: 0.3, Fty_E_eu_8: 0.24, Fty_E_eu_10: 0.19}, </v>
+      </c>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B81" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C81" t="str">
+        <f t="shared" ref="B81:J81" si="8">_xlfn.CONCAT(C$75,": ",C9, ", ")</f>
+        <v xml:space="preserve">Dw: 0.25, </v>
+      </c>
+      <c r="D81" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.7, </v>
+      </c>
+      <c r="E81" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.68, </v>
+      </c>
+      <c r="F81" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.63, </v>
+      </c>
+      <c r="G81" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.47, </v>
+      </c>
+      <c r="H81" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.36, </v>
+      </c>
+      <c r="I81" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.29, </v>
+      </c>
+      <c r="J81" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.24}, </v>
+      </c>
+      <c r="L81" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.25, Fty_E_eu_0: 0.7, Fty_E_eu_1: 0.68, Fty_E_eu_2: 0.63, Fty_E_eu_4: 0.47, Fty_E_eu_6: 0.36, Fty_E_eu_8: 0.29, Fty_E_eu_10: 0.24}, </v>
+      </c>
+    </row>
+    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B82" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C82" t="str">
+        <f t="shared" ref="B82:J82" si="9">_xlfn.CONCAT(C$75,": ",C10, ", ")</f>
+        <v xml:space="preserve">Dw: 0.3, </v>
+      </c>
+      <c r="D82" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.71, </v>
+      </c>
+      <c r="E82" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.69, </v>
+      </c>
+      <c r="F82" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.66, </v>
+      </c>
+      <c r="G82" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.53, </v>
+      </c>
+      <c r="H82" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.41, </v>
+      </c>
+      <c r="I82" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.33, </v>
+      </c>
+      <c r="J82" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.27}, </v>
+      </c>
+      <c r="L82" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.3, Fty_E_eu_0: 0.71, Fty_E_eu_1: 0.69, Fty_E_eu_2: 0.66, Fty_E_eu_4: 0.53, Fty_E_eu_6: 0.41, Fty_E_eu_8: 0.33, Fty_E_eu_10: 0.27}, </v>
+      </c>
+    </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B83" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C83" t="str">
+        <f t="shared" ref="B83:J83" si="10">_xlfn.CONCAT(C$75,": ",C11, ", ")</f>
+        <v xml:space="preserve">Dw: 0.35, </v>
+      </c>
+      <c r="D83" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.72, </v>
+      </c>
+      <c r="E83" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.7, </v>
+      </c>
+      <c r="F83" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.68, </v>
+      </c>
+      <c r="G83" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.57, </v>
+      </c>
+      <c r="H83" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.45, </v>
+      </c>
+      <c r="I83" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.37, </v>
+      </c>
+      <c r="J83" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.31}, </v>
+      </c>
+      <c r="L83" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.35, Fty_E_eu_0: 0.72, Fty_E_eu_1: 0.7, Fty_E_eu_2: 0.68, Fty_E_eu_4: 0.57, Fty_E_eu_6: 0.45, Fty_E_eu_8: 0.37, Fty_E_eu_10: 0.31}, </v>
+      </c>
+    </row>
+    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B84" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C84" t="str">
+        <f t="shared" ref="B84:J84" si="11">_xlfn.CONCAT(C$75,": ",C12, ", ")</f>
+        <v xml:space="preserve">Dw: 0.4, </v>
+      </c>
+      <c r="D84" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.73, </v>
+      </c>
+      <c r="E84" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.71, </v>
+      </c>
+      <c r="F84" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.69, </v>
+      </c>
+      <c r="G84" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.61, </v>
+      </c>
+      <c r="H84" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.49, </v>
+      </c>
+      <c r="I84" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.4, </v>
+      </c>
+      <c r="J84" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.34}, </v>
+      </c>
+      <c r="L84" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.4, Fty_E_eu_0: 0.73, Fty_E_eu_1: 0.71, Fty_E_eu_2: 0.69, Fty_E_eu_4: 0.61, Fty_E_eu_6: 0.49, Fty_E_eu_8: 0.4, Fty_E_eu_10: 0.34}, </v>
+      </c>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B85" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C85" t="str">
+        <f t="shared" ref="B85:J85" si="12">_xlfn.CONCAT(C$75,": ",C13, ", ")</f>
+        <v xml:space="preserve">Dw: 0.45, </v>
+      </c>
+      <c r="D85" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.74, </v>
+      </c>
+      <c r="E85" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.72, </v>
+      </c>
+      <c r="F85" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.7, </v>
+      </c>
+      <c r="G85" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.63, </v>
+      </c>
+      <c r="H85" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.53, </v>
+      </c>
+      <c r="I85" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.43, </v>
+      </c>
+      <c r="J85" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.36}, </v>
+      </c>
+      <c r="L85" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.45, Fty_E_eu_0: 0.74, Fty_E_eu_1: 0.72, Fty_E_eu_2: 0.7, Fty_E_eu_4: 0.63, Fty_E_eu_6: 0.53, Fty_E_eu_8: 0.43, Fty_E_eu_10: 0.36}, </v>
+      </c>
+    </row>
+    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B86" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C86" t="str">
+        <f t="shared" ref="B86:J86" si="13">_xlfn.CONCAT(C$75,": ",C14, ", ")</f>
+        <v xml:space="preserve">Dw: 0.5, </v>
+      </c>
+      <c r="D86" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.76, </v>
+      </c>
+      <c r="E86" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.74, </v>
+      </c>
+      <c r="F86" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.72, </v>
+      </c>
+      <c r="G86" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.64, </v>
+      </c>
+      <c r="H86" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.56, </v>
+      </c>
+      <c r="I86" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.46, </v>
+      </c>
+      <c r="J86" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.4}, </v>
+      </c>
+      <c r="L86" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.5, Fty_E_eu_0: 0.76, Fty_E_eu_1: 0.74, Fty_E_eu_2: 0.72, Fty_E_eu_4: 0.64, Fty_E_eu_6: 0.56, Fty_E_eu_8: 0.46, Fty_E_eu_10: 0.4}, </v>
+      </c>
+    </row>
+    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B87" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C87" t="str">
+        <f t="shared" ref="B87:J87" si="14">_xlfn.CONCAT(C$75,": ",C15, ", ")</f>
+        <v xml:space="preserve">Dw: 0.55, </v>
+      </c>
+      <c r="D87" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.77, </v>
+      </c>
+      <c r="E87" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.76, </v>
+      </c>
+      <c r="F87" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.73, </v>
+      </c>
+      <c r="G87" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.66, </v>
+      </c>
+      <c r="H87" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.59, </v>
+      </c>
+      <c r="I87" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.5, </v>
+      </c>
+      <c r="J87" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.43}, </v>
+      </c>
+      <c r="L87" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.55, Fty_E_eu_0: 0.77, Fty_E_eu_1: 0.76, Fty_E_eu_2: 0.73, Fty_E_eu_4: 0.66, Fty_E_eu_6: 0.59, Fty_E_eu_8: 0.5, Fty_E_eu_10: 0.43}, </v>
+      </c>
+    </row>
+    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B88" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C88" t="str">
+        <f t="shared" ref="B88:J88" si="15">_xlfn.CONCAT(C$75,": ",C16, ", ")</f>
+        <v xml:space="preserve">Dw: 0.6, </v>
+      </c>
+      <c r="D88" t="str">
+        <f t="shared" si="15"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.78, </v>
+      </c>
+      <c r="E88" t="str">
+        <f t="shared" si="15"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.77, </v>
+      </c>
+      <c r="F88" t="str">
+        <f t="shared" si="15"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.74, </v>
+      </c>
+      <c r="G88" t="str">
+        <f t="shared" si="15"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.68, </v>
+      </c>
+      <c r="H88" t="str">
+        <f t="shared" si="15"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.62, </v>
+      </c>
+      <c r="I88" t="str">
+        <f t="shared" si="15"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.53, </v>
+      </c>
+      <c r="J88" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.45}, </v>
+      </c>
+      <c r="L88" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.6, Fty_E_eu_0: 0.78, Fty_E_eu_1: 0.77, Fty_E_eu_2: 0.74, Fty_E_eu_4: 0.68, Fty_E_eu_6: 0.62, Fty_E_eu_8: 0.53, Fty_E_eu_10: 0.45}, </v>
+      </c>
+    </row>
+    <row r="89" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B89" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C89" t="str">
+        <f t="shared" ref="B89:J89" si="16">_xlfn.CONCAT(C$75,": ",C17, ", ")</f>
+        <v xml:space="preserve">Dw: 0.65, </v>
+      </c>
+      <c r="D89" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.8, </v>
+      </c>
+      <c r="E89" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.79, </v>
+      </c>
+      <c r="F89" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.77, </v>
+      </c>
+      <c r="G89" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.7, </v>
+      </c>
+      <c r="H89" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.64, </v>
+      </c>
+      <c r="I89" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.57, </v>
+      </c>
+      <c r="J89" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.49}, </v>
+      </c>
+      <c r="L89" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.65, Fty_E_eu_0: 0.8, Fty_E_eu_1: 0.79, Fty_E_eu_2: 0.77, Fty_E_eu_4: 0.7, Fty_E_eu_6: 0.64, Fty_E_eu_8: 0.57, Fty_E_eu_10: 0.49}, </v>
+      </c>
+    </row>
+    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C90" t="str">
+        <f t="shared" ref="B90:J90" si="17">_xlfn.CONCAT(C$75,": ",C18, ", ")</f>
+        <v xml:space="preserve">Dw: 0.7, </v>
+      </c>
+      <c r="D90" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.82, </v>
+      </c>
+      <c r="E90" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.81, </v>
+      </c>
+      <c r="F90" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.78, </v>
+      </c>
+      <c r="G90" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.73, </v>
+      </c>
+      <c r="H90" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.68, </v>
+      </c>
+      <c r="I90" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.61, </v>
+      </c>
+      <c r="J90" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.53}, </v>
+      </c>
+      <c r="L90" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.7, Fty_E_eu_0: 0.82, Fty_E_eu_1: 0.81, Fty_E_eu_2: 0.78, Fty_E_eu_4: 0.73, Fty_E_eu_6: 0.68, Fty_E_eu_8: 0.61, Fty_E_eu_10: 0.53}, </v>
+      </c>
+    </row>
+    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B91" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C91" t="str">
+        <f t="shared" ref="B91:J91" si="18">_xlfn.CONCAT(C$75,": ",C19, ", ")</f>
+        <v xml:space="preserve">Dw: 0.75, </v>
+      </c>
+      <c r="D91" t="str">
+        <f t="shared" si="18"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.84, </v>
+      </c>
+      <c r="E91" t="str">
+        <f t="shared" si="18"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.82, </v>
+      </c>
+      <c r="F91" t="str">
+        <f t="shared" si="18"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.81, </v>
+      </c>
+      <c r="G91" t="str">
+        <f t="shared" si="18"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.77, </v>
+      </c>
+      <c r="H91" t="str">
+        <f t="shared" si="18"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.72, </v>
+      </c>
+      <c r="I91" t="str">
+        <f t="shared" si="18"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.66, </v>
+      </c>
+      <c r="J91" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.58}, </v>
+      </c>
+      <c r="L91" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.75, Fty_E_eu_0: 0.84, Fty_E_eu_1: 0.82, Fty_E_eu_2: 0.81, Fty_E_eu_4: 0.77, Fty_E_eu_6: 0.72, Fty_E_eu_8: 0.66, Fty_E_eu_10: 0.58}, </v>
+      </c>
+    </row>
+    <row r="92" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B92" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C92" t="str">
+        <f t="shared" ref="B92:J92" si="19">_xlfn.CONCAT(C$75,": ",C20, ", ")</f>
+        <v xml:space="preserve">Dw: 0.8, </v>
+      </c>
+      <c r="D92" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.86, </v>
+      </c>
+      <c r="E92" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.84, </v>
+      </c>
+      <c r="F92" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.84, </v>
+      </c>
+      <c r="G92" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.8, </v>
+      </c>
+      <c r="H92" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.76, </v>
+      </c>
+      <c r="I92" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.71, </v>
+      </c>
+      <c r="J92" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.64}, </v>
+      </c>
+      <c r="L92" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.8, Fty_E_eu_0: 0.86, Fty_E_eu_1: 0.84, Fty_E_eu_2: 0.84, Fty_E_eu_4: 0.8, Fty_E_eu_6: 0.76, Fty_E_eu_8: 0.71, Fty_E_eu_10: 0.64}, </v>
+      </c>
+    </row>
+    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B93" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C93" t="str">
+        <f t="shared" ref="B93:J93" si="20">_xlfn.CONCAT(C$75,": ",C21, ", ")</f>
+        <v xml:space="preserve">Dw: 0.85, </v>
+      </c>
+      <c r="D93" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.88, </v>
+      </c>
+      <c r="E93" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.87, </v>
+      </c>
+      <c r="F93" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.87, </v>
+      </c>
+      <c r="G93" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.84, </v>
+      </c>
+      <c r="H93" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.81, </v>
+      </c>
+      <c r="I93" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.77, </v>
+      </c>
+      <c r="J93" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.71}, </v>
+      </c>
+      <c r="L93" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.85, Fty_E_eu_0: 0.88, Fty_E_eu_1: 0.87, Fty_E_eu_2: 0.87, Fty_E_eu_4: 0.84, Fty_E_eu_6: 0.81, Fty_E_eu_8: 0.77, Fty_E_eu_10: 0.71}, </v>
+      </c>
+    </row>
+    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B94" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C94" t="str">
+        <f t="shared" ref="B94:J94" si="21">_xlfn.CONCAT(C$75,": ",C22, ", ")</f>
+        <v xml:space="preserve">Dw: 0.9, </v>
+      </c>
+      <c r="D94" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.91, </v>
+      </c>
+      <c r="E94" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.9, </v>
+      </c>
+      <c r="F94" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.9, </v>
+      </c>
+      <c r="G94" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.88, </v>
+      </c>
+      <c r="H94" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.86, </v>
+      </c>
+      <c r="I94" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.83, </v>
+      </c>
+      <c r="J94" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.79}, </v>
+      </c>
+      <c r="L94" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.9, Fty_E_eu_0: 0.91, Fty_E_eu_1: 0.9, Fty_E_eu_2: 0.9, Fty_E_eu_4: 0.88, Fty_E_eu_6: 0.86, Fty_E_eu_8: 0.83, Fty_E_eu_10: 0.79}, </v>
+      </c>
+    </row>
+    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B95" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C95" t="str">
+        <f t="shared" ref="B95:J95" si="22">_xlfn.CONCAT(C$75,": ",C23, ", ")</f>
+        <v xml:space="preserve">Dw: 0.95, </v>
+      </c>
+      <c r="D95" t="str">
+        <f t="shared" si="22"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.95, </v>
+      </c>
+      <c r="E95" t="str">
+        <f t="shared" si="22"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.95, </v>
+      </c>
+      <c r="F95" t="str">
+        <f t="shared" si="22"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.95, </v>
+      </c>
+      <c r="G95" t="str">
+        <f t="shared" si="22"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.94, </v>
+      </c>
+      <c r="H95" t="str">
+        <f t="shared" si="22"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.94, </v>
+      </c>
+      <c r="I95" t="str">
+        <f t="shared" si="22"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.92, </v>
+      </c>
+      <c r="J95" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.89}, </v>
+      </c>
+      <c r="L95" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 0.95, Fty_E_eu_0: 0.95, Fty_E_eu_1: 0.95, Fty_E_eu_2: 0.95, Fty_E_eu_4: 0.94, Fty_E_eu_6: 0.94, Fty_E_eu_8: 0.92, Fty_E_eu_10: 0.89}, </v>
+      </c>
+    </row>
+    <row r="96" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B96" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, </v>
+      </c>
+      <c r="C96" t="str">
+        <f t="shared" ref="B96:J96" si="23">_xlfn.CONCAT(C$75,": ",C24, ", ")</f>
+        <v xml:space="preserve">Dw: 1, </v>
+      </c>
+      <c r="D96" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E96" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F96" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">Fty_E_eu_2: 1, </v>
+      </c>
+      <c r="G96" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">Fty_E_eu_4: 1, </v>
+      </c>
+      <c r="H96" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">Fty_E_eu_6: 1, </v>
+      </c>
+      <c r="I96" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">Fty_E_eu_8: 1, </v>
+      </c>
+      <c r="J96" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 1}, </v>
+      </c>
+      <c r="L96" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.6, Dw: 1, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 1, Fty_E_eu_4: 1, Fty_E_eu_6: 1, Fty_E_eu_8: 1, Fty_E_eu_10: 1}, </v>
+      </c>
+    </row>
+    <row r="97" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B97" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C97" t="str">
+        <f t="shared" ref="B97:J97" si="24">_xlfn.CONCAT(C$75,": ",C25, ", ")</f>
+        <v xml:space="preserve">Dw: 0, </v>
+      </c>
+      <c r="D97" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0, </v>
+      </c>
+      <c r="E97" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0, </v>
+      </c>
+      <c r="F97" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0, </v>
+      </c>
+      <c r="G97" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0, </v>
+      </c>
+      <c r="H97" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0, </v>
+      </c>
+      <c r="I97" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0, </v>
+      </c>
+      <c r="J97" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0}, </v>
+      </c>
+      <c r="L97" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0, Fty_E_eu_0: 0, Fty_E_eu_1: 0, Fty_E_eu_2: 0, Fty_E_eu_4: 0, Fty_E_eu_6: 0, Fty_E_eu_8: 0, Fty_E_eu_10: 0}, </v>
+      </c>
+    </row>
+    <row r="98" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B98" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C98" t="str">
+        <f t="shared" ref="B98:J98" si="25">_xlfn.CONCAT(C$75,": ",C26, ", ")</f>
+        <v xml:space="preserve">Dw: 0.05, </v>
+      </c>
+      <c r="D98" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.4, </v>
+      </c>
+      <c r="E98" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.38, </v>
+      </c>
+      <c r="F98" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.24, </v>
+      </c>
+      <c r="G98" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.14, </v>
+      </c>
+      <c r="H98" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.08, </v>
+      </c>
+      <c r="I98" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.07, </v>
+      </c>
+      <c r="J98" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.05}, </v>
+      </c>
+      <c r="L98" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.05, Fty_E_eu_0: 0.4, Fty_E_eu_1: 0.38, Fty_E_eu_2: 0.24, Fty_E_eu_4: 0.14, Fty_E_eu_6: 0.08, Fty_E_eu_8: 0.07, Fty_E_eu_10: 0.05}, </v>
+      </c>
+    </row>
+    <row r="99" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B99" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C99" t="str">
+        <f t="shared" ref="B99:J99" si="26">_xlfn.CONCAT(C$75,": ",C27, ", ")</f>
+        <v xml:space="preserve">Dw: 0.1, </v>
+      </c>
+      <c r="D99" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.66, </v>
+      </c>
+      <c r="E99" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.59, </v>
+      </c>
+      <c r="F99" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.42, </v>
+      </c>
+      <c r="G99" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.25, </v>
+      </c>
+      <c r="H99" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.15, </v>
+      </c>
+      <c r="I99" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.12, </v>
+      </c>
+      <c r="J99" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.1}, </v>
+      </c>
+      <c r="L99" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.1, Fty_E_eu_0: 0.66, Fty_E_eu_1: 0.59, Fty_E_eu_2: 0.42, Fty_E_eu_4: 0.25, Fty_E_eu_6: 0.15, Fty_E_eu_8: 0.12, Fty_E_eu_10: 0.1}, </v>
+      </c>
+    </row>
+    <row r="100" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B100" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C100" t="str">
+        <f t="shared" ref="B100:J100" si="27">_xlfn.CONCAT(C$75,": ",C28, ", ")</f>
+        <v xml:space="preserve">Dw: 0.15, </v>
+      </c>
+      <c r="D100" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.79, </v>
+      </c>
+      <c r="E100" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.73, </v>
+      </c>
+      <c r="F100" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.56, </v>
+      </c>
+      <c r="G100" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.35, </v>
+      </c>
+      <c r="H100" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.22, </v>
+      </c>
+      <c r="I100" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.18, </v>
+      </c>
+      <c r="J100" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.15}, </v>
+      </c>
+      <c r="L100" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.15, Fty_E_eu_0: 0.79, Fty_E_eu_1: 0.73, Fty_E_eu_2: 0.56, Fty_E_eu_4: 0.35, Fty_E_eu_6: 0.22, Fty_E_eu_8: 0.18, Fty_E_eu_10: 0.15}, </v>
+      </c>
+    </row>
+    <row r="101" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B101" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C101" t="str">
+        <f t="shared" ref="B101:J101" si="28">_xlfn.CONCAT(C$75,": ",C29, ", ")</f>
+        <v xml:space="preserve">Dw: 0.2, </v>
+      </c>
+      <c r="D101" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.83, </v>
+      </c>
+      <c r="E101" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.81, </v>
+      </c>
+      <c r="F101" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.67, </v>
+      </c>
+      <c r="G101" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.43, </v>
+      </c>
+      <c r="H101" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.29, </v>
+      </c>
+      <c r="I101" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.23, </v>
+      </c>
+      <c r="J101" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.19}, </v>
+      </c>
+      <c r="L101" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.2, Fty_E_eu_0: 0.83, Fty_E_eu_1: 0.81, Fty_E_eu_2: 0.67, Fty_E_eu_4: 0.43, Fty_E_eu_6: 0.29, Fty_E_eu_8: 0.23, Fty_E_eu_10: 0.19}, </v>
+      </c>
+    </row>
+    <row r="102" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B102" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C102" t="str">
+        <f t="shared" ref="B102:J102" si="29">_xlfn.CONCAT(C$75,": ",C30, ", ")</f>
+        <v xml:space="preserve">Dw: 0.25, </v>
+      </c>
+      <c r="D102" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.84, </v>
+      </c>
+      <c r="E102" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.83, </v>
+      </c>
+      <c r="F102" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.74, </v>
+      </c>
+      <c r="G102" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.5, </v>
+      </c>
+      <c r="H102" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.36, </v>
+      </c>
+      <c r="I102" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.28, </v>
+      </c>
+      <c r="J102" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.24}, </v>
+      </c>
+      <c r="L102" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.25, Fty_E_eu_0: 0.84, Fty_E_eu_1: 0.83, Fty_E_eu_2: 0.74, Fty_E_eu_4: 0.5, Fty_E_eu_6: 0.36, Fty_E_eu_8: 0.28, Fty_E_eu_10: 0.24}, </v>
+      </c>
+    </row>
+    <row r="103" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B103" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C103" t="str">
+        <f t="shared" ref="B103:J103" si="30">_xlfn.CONCAT(C$75,": ",C31, ", ")</f>
+        <v xml:space="preserve">Dw: 0.3, </v>
+      </c>
+      <c r="D103" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.85, </v>
+      </c>
+      <c r="E103" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.84, </v>
+      </c>
+      <c r="F103" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.77, </v>
+      </c>
+      <c r="G103" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.56, </v>
+      </c>
+      <c r="H103" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.42, </v>
+      </c>
+      <c r="I103" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.33, </v>
+      </c>
+      <c r="J103" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.28}, </v>
+      </c>
+      <c r="L103" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.3, Fty_E_eu_0: 0.85, Fty_E_eu_1: 0.84, Fty_E_eu_2: 0.77, Fty_E_eu_4: 0.56, Fty_E_eu_6: 0.42, Fty_E_eu_8: 0.33, Fty_E_eu_10: 0.28}, </v>
+      </c>
+    </row>
+    <row r="104" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B104" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C104" t="str">
+        <f t="shared" ref="B104:J104" si="31">_xlfn.CONCAT(C$75,": ",C32, ", ")</f>
+        <v xml:space="preserve">Dw: 0.35, </v>
+      </c>
+      <c r="D104" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.85, </v>
+      </c>
+      <c r="E104" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.85, </v>
+      </c>
+      <c r="F104" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.8, </v>
+      </c>
+      <c r="G104" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.62, </v>
+      </c>
+      <c r="H104" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.48, </v>
+      </c>
+      <c r="I104" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.37, </v>
+      </c>
+      <c r="J104" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.31}, </v>
+      </c>
+      <c r="L104" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.35, Fty_E_eu_0: 0.85, Fty_E_eu_1: 0.85, Fty_E_eu_2: 0.8, Fty_E_eu_4: 0.62, Fty_E_eu_6: 0.48, Fty_E_eu_8: 0.37, Fty_E_eu_10: 0.31}, </v>
+      </c>
+    </row>
+    <row r="105" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B105" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C105" t="str">
+        <f t="shared" ref="B105:J105" si="32">_xlfn.CONCAT(C$75,": ",C33, ", ")</f>
+        <v xml:space="preserve">Dw: 0.4, </v>
+      </c>
+      <c r="D105" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.86, </v>
+      </c>
+      <c r="E105" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.86, </v>
+      </c>
+      <c r="F105" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.81, </v>
+      </c>
+      <c r="G105" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.66, </v>
+      </c>
+      <c r="H105" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.52, </v>
+      </c>
+      <c r="I105" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.41, </v>
+      </c>
+      <c r="J105" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.34}, </v>
+      </c>
+      <c r="L105" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.4, Fty_E_eu_0: 0.86, Fty_E_eu_1: 0.86, Fty_E_eu_2: 0.81, Fty_E_eu_4: 0.66, Fty_E_eu_6: 0.52, Fty_E_eu_8: 0.41, Fty_E_eu_10: 0.34}, </v>
+      </c>
+    </row>
+    <row r="106" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B106" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C106" t="str">
+        <f t="shared" ref="B106:J106" si="33">_xlfn.CONCAT(C$75,": ",C34, ", ")</f>
+        <v xml:space="preserve">Dw: 0.45, </v>
+      </c>
+      <c r="D106" t="str">
+        <f t="shared" si="33"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.86, </v>
+      </c>
+      <c r="E106" t="str">
+        <f t="shared" si="33"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.86, </v>
+      </c>
+      <c r="F106" t="str">
+        <f t="shared" si="33"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.83, </v>
+      </c>
+      <c r="G106" t="str">
+        <f t="shared" si="33"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.69, </v>
+      </c>
+      <c r="H106" t="str">
+        <f t="shared" si="33"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.56, </v>
+      </c>
+      <c r="I106" t="str">
+        <f t="shared" si="33"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.44, </v>
+      </c>
+      <c r="J106" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.37}, </v>
+      </c>
+      <c r="L106" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.45, Fty_E_eu_0: 0.86, Fty_E_eu_1: 0.86, Fty_E_eu_2: 0.83, Fty_E_eu_4: 0.69, Fty_E_eu_6: 0.56, Fty_E_eu_8: 0.44, Fty_E_eu_10: 0.37}, </v>
+      </c>
+    </row>
+    <row r="107" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B107" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C107" t="str">
+        <f t="shared" ref="B107:J107" si="34">_xlfn.CONCAT(C$75,": ",C35, ", ")</f>
+        <v xml:space="preserve">Dw: 0.5, </v>
+      </c>
+      <c r="D107" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.87, </v>
+      </c>
+      <c r="E107" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.87, </v>
+      </c>
+      <c r="F107" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.84, </v>
+      </c>
+      <c r="G107" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.72, </v>
+      </c>
+      <c r="H107" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.59, </v>
+      </c>
+      <c r="I107" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.47, </v>
+      </c>
+      <c r="J107" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.4}, </v>
+      </c>
+      <c r="L107" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.5, Fty_E_eu_0: 0.87, Fty_E_eu_1: 0.87, Fty_E_eu_2: 0.84, Fty_E_eu_4: 0.72, Fty_E_eu_6: 0.59, Fty_E_eu_8: 0.47, Fty_E_eu_10: 0.4}, </v>
+      </c>
+    </row>
+    <row r="108" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B108" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C108" t="str">
+        <f t="shared" ref="B108:J108" si="35">_xlfn.CONCAT(C$75,": ",C36, ", ")</f>
+        <v xml:space="preserve">Dw: 0.55, </v>
+      </c>
+      <c r="D108" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.88, </v>
+      </c>
+      <c r="E108" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.88, </v>
+      </c>
+      <c r="F108" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.84, </v>
+      </c>
+      <c r="G108" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.74, </v>
+      </c>
+      <c r="H108" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.62, </v>
+      </c>
+      <c r="I108" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.51, </v>
+      </c>
+      <c r="J108" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.44}, </v>
+      </c>
+      <c r="L108" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.55, Fty_E_eu_0: 0.88, Fty_E_eu_1: 0.88, Fty_E_eu_2: 0.84, Fty_E_eu_4: 0.74, Fty_E_eu_6: 0.62, Fty_E_eu_8: 0.51, Fty_E_eu_10: 0.44}, </v>
+      </c>
+    </row>
+    <row r="109" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B109" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C109" t="str">
+        <f t="shared" ref="B109:J109" si="36">_xlfn.CONCAT(C$75,": ",C37, ", ")</f>
+        <v xml:space="preserve">Dw: 0.6, </v>
+      </c>
+      <c r="D109" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.89, </v>
+      </c>
+      <c r="E109" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.89, </v>
+      </c>
+      <c r="F109" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.85, </v>
+      </c>
+      <c r="G109" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.76, </v>
+      </c>
+      <c r="H109" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.65, </v>
+      </c>
+      <c r="I109" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.55, </v>
+      </c>
+      <c r="J109" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.47}, </v>
+      </c>
+      <c r="L109" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.6, Fty_E_eu_0: 0.89, Fty_E_eu_1: 0.89, Fty_E_eu_2: 0.85, Fty_E_eu_4: 0.76, Fty_E_eu_6: 0.65, Fty_E_eu_8: 0.55, Fty_E_eu_10: 0.47}, </v>
+      </c>
+    </row>
+    <row r="110" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B110" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C110" t="str">
+        <f t="shared" ref="B110:J110" si="37">_xlfn.CONCAT(C$75,": ",C38, ", ")</f>
+        <v xml:space="preserve">Dw: 0.65, </v>
+      </c>
+      <c r="D110" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.9, </v>
+      </c>
+      <c r="E110" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.9, </v>
+      </c>
+      <c r="F110" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.86, </v>
+      </c>
+      <c r="G110" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.79, </v>
+      </c>
+      <c r="H110" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.68, </v>
+      </c>
+      <c r="I110" t="str">
+        <f t="shared" si="37"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.58, </v>
+      </c>
+      <c r="J110" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.5}, </v>
+      </c>
+      <c r="L110" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.65, Fty_E_eu_0: 0.9, Fty_E_eu_1: 0.9, Fty_E_eu_2: 0.86, Fty_E_eu_4: 0.79, Fty_E_eu_6: 0.68, Fty_E_eu_8: 0.58, Fty_E_eu_10: 0.5}, </v>
+      </c>
+    </row>
+    <row r="111" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B111" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C111" t="str">
+        <f t="shared" ref="B111:J111" si="38">_xlfn.CONCAT(C$75,": ",C39, ", ")</f>
+        <v xml:space="preserve">Dw: 0.7, </v>
+      </c>
+      <c r="D111" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.9, </v>
+      </c>
+      <c r="E111" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.9, </v>
+      </c>
+      <c r="F111" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.87, </v>
+      </c>
+      <c r="G111" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.82, </v>
+      </c>
+      <c r="H111" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.72, </v>
+      </c>
+      <c r="I111" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.63, </v>
+      </c>
+      <c r="J111" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.53}, </v>
+      </c>
+      <c r="L111" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.7, Fty_E_eu_0: 0.9, Fty_E_eu_1: 0.9, Fty_E_eu_2: 0.87, Fty_E_eu_4: 0.82, Fty_E_eu_6: 0.72, Fty_E_eu_8: 0.63, Fty_E_eu_10: 0.53}, </v>
+      </c>
+    </row>
+    <row r="112" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B112" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C112" t="str">
+        <f t="shared" ref="B112:J112" si="39">_xlfn.CONCAT(C$75,": ",C40, ", ")</f>
+        <v xml:space="preserve">Dw: 0.75, </v>
+      </c>
+      <c r="D112" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.91, </v>
+      </c>
+      <c r="E112" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.91, </v>
+      </c>
+      <c r="F112" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.89, </v>
+      </c>
+      <c r="G112" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.84, </v>
+      </c>
+      <c r="H112" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.77, </v>
+      </c>
+      <c r="I112" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.69, </v>
+      </c>
+      <c r="J112" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.58}, </v>
+      </c>
+      <c r="L112" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.75, Fty_E_eu_0: 0.91, Fty_E_eu_1: 0.91, Fty_E_eu_2: 0.89, Fty_E_eu_4: 0.84, Fty_E_eu_6: 0.77, Fty_E_eu_8: 0.69, Fty_E_eu_10: 0.58}, </v>
+      </c>
+    </row>
+    <row r="113" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B113" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C113" t="str">
+        <f t="shared" ref="B113:J113" si="40">_xlfn.CONCAT(C$75,": ",C41, ", ")</f>
+        <v xml:space="preserve">Dw: 0.8, </v>
+      </c>
+      <c r="D113" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.92, </v>
+      </c>
+      <c r="E113" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.92, </v>
+      </c>
+      <c r="F113" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.92, </v>
+      </c>
+      <c r="G113" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.88, </v>
+      </c>
+      <c r="H113" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.83, </v>
+      </c>
+      <c r="I113" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.74, </v>
+      </c>
+      <c r="J113" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.64}, </v>
+      </c>
+      <c r="L113" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.8, Fty_E_eu_0: 0.92, Fty_E_eu_1: 0.92, Fty_E_eu_2: 0.92, Fty_E_eu_4: 0.88, Fty_E_eu_6: 0.83, Fty_E_eu_8: 0.74, Fty_E_eu_10: 0.64}, </v>
+      </c>
+    </row>
+    <row r="114" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B114" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C114" t="str">
+        <f t="shared" ref="B114:J114" si="41">_xlfn.CONCAT(C$75,": ",C42, ", ")</f>
+        <v xml:space="preserve">Dw: 0.85, </v>
+      </c>
+      <c r="D114" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.94, </v>
+      </c>
+      <c r="E114" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.94, </v>
+      </c>
+      <c r="F114" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.94, </v>
+      </c>
+      <c r="G114" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.91, </v>
+      </c>
+      <c r="H114" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.87, </v>
+      </c>
+      <c r="I114" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.79, </v>
+      </c>
+      <c r="J114" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.71}, </v>
+      </c>
+      <c r="L114" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.85, Fty_E_eu_0: 0.94, Fty_E_eu_1: 0.94, Fty_E_eu_2: 0.94, Fty_E_eu_4: 0.91, Fty_E_eu_6: 0.87, Fty_E_eu_8: 0.79, Fty_E_eu_10: 0.71}, </v>
+      </c>
+    </row>
+    <row r="115" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B115" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C115" t="str">
+        <f t="shared" ref="B115:J115" si="42">_xlfn.CONCAT(C$75,": ",C43, ", ")</f>
+        <v xml:space="preserve">Dw: 0.9, </v>
+      </c>
+      <c r="D115" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.96, </v>
+      </c>
+      <c r="E115" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.96, </v>
+      </c>
+      <c r="F115" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.96, </v>
+      </c>
+      <c r="G115" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.94, </v>
+      </c>
+      <c r="H115" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.91, </v>
+      </c>
+      <c r="I115" t="str">
+        <f t="shared" si="42"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.85, </v>
+      </c>
+      <c r="J115" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.79}, </v>
+      </c>
+      <c r="L115" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.9, Fty_E_eu_0: 0.96, Fty_E_eu_1: 0.96, Fty_E_eu_2: 0.96, Fty_E_eu_4: 0.94, Fty_E_eu_6: 0.91, Fty_E_eu_8: 0.85, Fty_E_eu_10: 0.79}, </v>
+      </c>
+    </row>
+    <row r="116" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B116" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C116" t="str">
+        <f t="shared" ref="B116:J116" si="43">_xlfn.CONCAT(C$75,": ",C44, ", ")</f>
+        <v xml:space="preserve">Dw: 0.95, </v>
+      </c>
+      <c r="D116" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.97, </v>
+      </c>
+      <c r="E116" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.97, </v>
+      </c>
+      <c r="F116" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.97, </v>
+      </c>
+      <c r="G116" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.97, </v>
+      </c>
+      <c r="H116" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.95, </v>
+      </c>
+      <c r="I116" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.92, </v>
+      </c>
+      <c r="J116" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.88}, </v>
+      </c>
+      <c r="L116" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 0.95, Fty_E_eu_0: 0.97, Fty_E_eu_1: 0.97, Fty_E_eu_2: 0.97, Fty_E_eu_4: 0.97, Fty_E_eu_6: 0.95, Fty_E_eu_8: 0.92, Fty_E_eu_10: 0.88}, </v>
+      </c>
+    </row>
+    <row r="117" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B117" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, </v>
+      </c>
+      <c r="C117" t="str">
+        <f t="shared" ref="B117:J117" si="44">_xlfn.CONCAT(C$75,": ",C45, ", ")</f>
+        <v xml:space="preserve">Dw: 1, </v>
+      </c>
+      <c r="D117" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E117" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F117" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">Fty_E_eu_2: 1, </v>
+      </c>
+      <c r="G117" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">Fty_E_eu_4: 1, </v>
+      </c>
+      <c r="H117" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">Fty_E_eu_6: 1, </v>
+      </c>
+      <c r="I117" t="str">
+        <f t="shared" si="44"/>
+        <v xml:space="preserve">Fty_E_eu_8: 1, </v>
+      </c>
+      <c r="J117" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 1}, </v>
+      </c>
+      <c r="L117" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 0.8, Dw: 1, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 1, Fty_E_eu_4: 1, Fty_E_eu_6: 1, Fty_E_eu_8: 1, Fty_E_eu_10: 1}, </v>
+      </c>
+    </row>
+    <row r="118" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B118" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C118" t="str">
+        <f t="shared" ref="B118:J118" si="45">_xlfn.CONCAT(C$75,": ",C46, ", ")</f>
+        <v xml:space="preserve">Dw: 0, </v>
+      </c>
+      <c r="D118" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0, </v>
+      </c>
+      <c r="E118" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0, </v>
+      </c>
+      <c r="F118" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0, </v>
+      </c>
+      <c r="G118" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0, </v>
+      </c>
+      <c r="H118" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0, </v>
+      </c>
+      <c r="I118" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0, </v>
+      </c>
+      <c r="J118" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0}, </v>
+      </c>
+      <c r="L118" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0, Fty_E_eu_0: 0, Fty_E_eu_1: 0, Fty_E_eu_2: 0, Fty_E_eu_4: 0, Fty_E_eu_6: 0, Fty_E_eu_8: 0, Fty_E_eu_10: 0}, </v>
+      </c>
+    </row>
+    <row r="119" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B119" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C119" t="str">
+        <f t="shared" ref="B119:J119" si="46">_xlfn.CONCAT(C$75,": ",C47, ", ")</f>
+        <v xml:space="preserve">Dw: 0.05, </v>
+      </c>
+      <c r="D119" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.54, </v>
+      </c>
+      <c r="E119" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.44, </v>
+      </c>
+      <c r="F119" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.26, </v>
+      </c>
+      <c r="G119" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.13, </v>
+      </c>
+      <c r="H119" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.09, </v>
+      </c>
+      <c r="I119" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.07, </v>
+      </c>
+      <c r="J119" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.06}, </v>
+      </c>
+      <c r="L119" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.05, Fty_E_eu_0: 0.54, Fty_E_eu_1: 0.44, Fty_E_eu_2: 0.26, Fty_E_eu_4: 0.13, Fty_E_eu_6: 0.09, Fty_E_eu_8: 0.07, Fty_E_eu_10: 0.06}, </v>
+      </c>
+    </row>
+    <row r="120" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B120" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C120" t="str">
+        <f t="shared" ref="B120:J120" si="47">_xlfn.CONCAT(C$75,": ",C48, ", ")</f>
+        <v xml:space="preserve">Dw: 0.1, </v>
+      </c>
+      <c r="D120" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.78, </v>
+      </c>
+      <c r="E120" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.69, </v>
+      </c>
+      <c r="F120" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.44, </v>
+      </c>
+      <c r="G120" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.22, </v>
+      </c>
+      <c r="H120" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.16, </v>
+      </c>
+      <c r="I120" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.13, </v>
+      </c>
+      <c r="J120" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.12}, </v>
+      </c>
+      <c r="L120" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.1, Fty_E_eu_0: 0.78, Fty_E_eu_1: 0.69, Fty_E_eu_2: 0.44, Fty_E_eu_4: 0.22, Fty_E_eu_6: 0.16, Fty_E_eu_8: 0.13, Fty_E_eu_10: 0.12}, </v>
+      </c>
+    </row>
+    <row r="121" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B121" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C121" t="str">
+        <f t="shared" ref="B121:J121" si="48">_xlfn.CONCAT(C$75,": ",C49, ", ")</f>
+        <v xml:space="preserve">Dw: 0.15, </v>
+      </c>
+      <c r="D121" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">Fty_E_eu_0: 0.93, </v>
+      </c>
+      <c r="E121" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.86, </v>
+      </c>
+      <c r="F121" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.58, </v>
+      </c>
+      <c r="G121" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.31, </v>
+      </c>
+      <c r="H121" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.23, </v>
+      </c>
+      <c r="I121" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.18, </v>
+      </c>
+      <c r="J121" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.16}, </v>
+      </c>
+      <c r="L121" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.15, Fty_E_eu_0: 0.93, Fty_E_eu_1: 0.86, Fty_E_eu_2: 0.58, Fty_E_eu_4: 0.31, Fty_E_eu_6: 0.23, Fty_E_eu_8: 0.18, Fty_E_eu_10: 0.16}, </v>
+      </c>
+    </row>
+    <row r="122" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B122" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C122" t="str">
+        <f t="shared" ref="B122:J122" si="49">_xlfn.CONCAT(C$75,": ",C50, ", ")</f>
+        <v xml:space="preserve">Dw: 0.2, </v>
+      </c>
+      <c r="D122" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E122" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.96, </v>
+      </c>
+      <c r="F122" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.71, </v>
+      </c>
+      <c r="G122" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.42, </v>
+      </c>
+      <c r="H122" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.3, </v>
+      </c>
+      <c r="I122" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.23, </v>
+      </c>
+      <c r="J122" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.2}, </v>
+      </c>
+      <c r="L122" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.2, Fty_E_eu_0: 1, Fty_E_eu_1: 0.96, Fty_E_eu_2: 0.71, Fty_E_eu_4: 0.42, Fty_E_eu_6: 0.3, Fty_E_eu_8: 0.23, Fty_E_eu_10: 0.2}, </v>
+      </c>
+    </row>
+    <row r="123" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B123" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C123" t="str">
+        <f t="shared" ref="B123:J123" si="50">_xlfn.CONCAT(C$75,": ",C51, ", ")</f>
+        <v xml:space="preserve">Dw: 0.25, </v>
+      </c>
+      <c r="D123" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E123" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.98, </v>
+      </c>
+      <c r="F123" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.8, </v>
+      </c>
+      <c r="G123" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.5, </v>
+      </c>
+      <c r="H123" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.36, </v>
+      </c>
+      <c r="I123" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.28, </v>
+      </c>
+      <c r="J123" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.24}, </v>
+      </c>
+      <c r="L123" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.25, Fty_E_eu_0: 1, Fty_E_eu_1: 0.98, Fty_E_eu_2: 0.8, Fty_E_eu_4: 0.5, Fty_E_eu_6: 0.36, Fty_E_eu_8: 0.28, Fty_E_eu_10: 0.24}, </v>
+      </c>
+    </row>
+    <row r="124" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B124" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C124" t="str">
+        <f t="shared" ref="B124:J124" si="51">_xlfn.CONCAT(C$75,": ",C52, ", ")</f>
+        <v xml:space="preserve">Dw: 0.3, </v>
+      </c>
+      <c r="D124" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E124" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.99, </v>
+      </c>
+      <c r="F124" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.87, </v>
+      </c>
+      <c r="G124" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.6, </v>
+      </c>
+      <c r="H124" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.42, </v>
+      </c>
+      <c r="I124" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.33, </v>
+      </c>
+      <c r="J124" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.28}, </v>
+      </c>
+      <c r="L124" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.3, Fty_E_eu_0: 1, Fty_E_eu_1: 0.99, Fty_E_eu_2: 0.87, Fty_E_eu_4: 0.6, Fty_E_eu_6: 0.42, Fty_E_eu_8: 0.33, Fty_E_eu_10: 0.28}, </v>
+      </c>
+    </row>
+    <row r="125" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B125" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C125" t="str">
+        <f t="shared" ref="B125:J125" si="52">_xlfn.CONCAT(C$75,": ",C53, ", ")</f>
+        <v xml:space="preserve">Dw: 0.35, </v>
+      </c>
+      <c r="D125" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E125" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">Fty_E_eu_1: 0.99, </v>
+      </c>
+      <c r="F125" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.93, </v>
+      </c>
+      <c r="G125" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.66, </v>
+      </c>
+      <c r="H125" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.48, </v>
+      </c>
+      <c r="I125" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.37, </v>
+      </c>
+      <c r="J125" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.31}, </v>
+      </c>
+      <c r="L125" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.35, Fty_E_eu_0: 1, Fty_E_eu_1: 0.99, Fty_E_eu_2: 0.93, Fty_E_eu_4: 0.66, Fty_E_eu_6: 0.48, Fty_E_eu_8: 0.37, Fty_E_eu_10: 0.31}, </v>
+      </c>
+    </row>
+    <row r="126" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B126" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C126" t="str">
+        <f t="shared" ref="B126:J126" si="53">_xlfn.CONCAT(C$75,": ",C54, ", ")</f>
+        <v xml:space="preserve">Dw: 0.4, </v>
+      </c>
+      <c r="D126" t="str">
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E126" t="str">
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F126" t="str">
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.96, </v>
+      </c>
+      <c r="G126" t="str">
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.71, </v>
+      </c>
+      <c r="H126" t="str">
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.53, </v>
+      </c>
+      <c r="I126" t="str">
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.41, </v>
+      </c>
+      <c r="J126" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.34}, </v>
+      </c>
+      <c r="L126" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.4, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.96, Fty_E_eu_4: 0.71, Fty_E_eu_6: 0.53, Fty_E_eu_8: 0.41, Fty_E_eu_10: 0.34}, </v>
+      </c>
+    </row>
+    <row r="127" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B127" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C127" t="str">
+        <f t="shared" ref="B127:J127" si="54">_xlfn.CONCAT(C$75,": ",C55, ", ")</f>
+        <v xml:space="preserve">Dw: 0.45, </v>
+      </c>
+      <c r="D127" t="str">
+        <f t="shared" si="54"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E127" t="str">
+        <f t="shared" si="54"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F127" t="str">
+        <f t="shared" si="54"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.97, </v>
+      </c>
+      <c r="G127" t="str">
+        <f t="shared" si="54"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.75, </v>
+      </c>
+      <c r="H127" t="str">
+        <f t="shared" si="54"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.58, </v>
+      </c>
+      <c r="I127" t="str">
+        <f t="shared" si="54"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.45, </v>
+      </c>
+      <c r="J127" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.37}, </v>
+      </c>
+      <c r="L127" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.45, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.97, Fty_E_eu_4: 0.75, Fty_E_eu_6: 0.58, Fty_E_eu_8: 0.45, Fty_E_eu_10: 0.37}, </v>
+      </c>
+    </row>
+    <row r="128" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B128" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C128" t="str">
+        <f t="shared" ref="B128:J128" si="55">_xlfn.CONCAT(C$75,": ",C56, ", ")</f>
+        <v xml:space="preserve">Dw: 0.5, </v>
+      </c>
+      <c r="D128" t="str">
+        <f t="shared" si="55"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E128" t="str">
+        <f t="shared" si="55"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F128" t="str">
+        <f t="shared" si="55"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.96, </v>
+      </c>
+      <c r="G128" t="str">
+        <f t="shared" si="55"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.78, </v>
+      </c>
+      <c r="H128" t="str">
+        <f t="shared" si="55"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.62, </v>
+      </c>
+      <c r="I128" t="str">
+        <f t="shared" si="55"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.49, </v>
+      </c>
+      <c r="J128" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.4}, </v>
+      </c>
+      <c r="L128" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.5, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.96, Fty_E_eu_4: 0.78, Fty_E_eu_6: 0.62, Fty_E_eu_8: 0.49, Fty_E_eu_10: 0.4}, </v>
+      </c>
+    </row>
+    <row r="129" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B129" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C129" t="str">
+        <f t="shared" ref="B129:J129" si="56">_xlfn.CONCAT(C$75,": ",C57, ", ")</f>
+        <v xml:space="preserve">Dw: 0.55, </v>
+      </c>
+      <c r="D129" t="str">
+        <f t="shared" si="56"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E129" t="str">
+        <f t="shared" si="56"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F129" t="str">
+        <f t="shared" si="56"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.96, </v>
+      </c>
+      <c r="G129" t="str">
+        <f t="shared" si="56"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.8, </v>
+      </c>
+      <c r="H129" t="str">
+        <f t="shared" si="56"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.66, </v>
+      </c>
+      <c r="I129" t="str">
+        <f t="shared" si="56"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.53, </v>
+      </c>
+      <c r="J129" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.43}, </v>
+      </c>
+      <c r="L129" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.55, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.96, Fty_E_eu_4: 0.8, Fty_E_eu_6: 0.66, Fty_E_eu_8: 0.53, Fty_E_eu_10: 0.43}, </v>
+      </c>
+    </row>
+    <row r="130" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B130" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C130" t="str">
+        <f t="shared" ref="B130:J130" si="57">_xlfn.CONCAT(C$75,": ",C58, ", ")</f>
+        <v xml:space="preserve">Dw: 0.6, </v>
+      </c>
+      <c r="D130" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E130" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F130" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.96, </v>
+      </c>
+      <c r="G130" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.83, </v>
+      </c>
+      <c r="H130" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.69, </v>
+      </c>
+      <c r="I130" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.56, </v>
+      </c>
+      <c r="J130" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.46}, </v>
+      </c>
+      <c r="L130" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.6, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.96, Fty_E_eu_4: 0.83, Fty_E_eu_6: 0.69, Fty_E_eu_8: 0.56, Fty_E_eu_10: 0.46}, </v>
+      </c>
+    </row>
+    <row r="131" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B131" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C131" t="str">
+        <f t="shared" ref="B131:J131" si="58">_xlfn.CONCAT(C$75,": ",C59, ", ")</f>
+        <v xml:space="preserve">Dw: 0.65, </v>
+      </c>
+      <c r="D131" t="str">
+        <f t="shared" si="58"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E131" t="str">
+        <f t="shared" si="58"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F131" t="str">
+        <f t="shared" si="58"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.96, </v>
+      </c>
+      <c r="G131" t="str">
+        <f t="shared" si="58"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.87, </v>
+      </c>
+      <c r="H131" t="str">
+        <f t="shared" si="58"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.73, </v>
+      </c>
+      <c r="I131" t="str">
+        <f t="shared" si="58"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.6, </v>
+      </c>
+      <c r="J131" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.5}, </v>
+      </c>
+      <c r="L131" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.65, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.96, Fty_E_eu_4: 0.87, Fty_E_eu_6: 0.73, Fty_E_eu_8: 0.6, Fty_E_eu_10: 0.5}, </v>
+      </c>
+    </row>
+    <row r="132" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B132" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C132" t="str">
+        <f t="shared" ref="B132:J132" si="59">_xlfn.CONCAT(C$75,": ",C60, ", ")</f>
+        <v xml:space="preserve">Dw: 0.7, </v>
+      </c>
+      <c r="D132" t="str">
+        <f t="shared" si="59"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E132" t="str">
+        <f t="shared" si="59"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F132" t="str">
+        <f t="shared" si="59"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.97, </v>
+      </c>
+      <c r="G132" t="str">
+        <f t="shared" si="59"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.9, </v>
+      </c>
+      <c r="H132" t="str">
+        <f t="shared" si="59"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.78, </v>
+      </c>
+      <c r="I132" t="str">
+        <f t="shared" si="59"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.64, </v>
+      </c>
+      <c r="J132" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.53}, </v>
+      </c>
+      <c r="L132" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.7, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.97, Fty_E_eu_4: 0.9, Fty_E_eu_6: 0.78, Fty_E_eu_8: 0.64, Fty_E_eu_10: 0.53}, </v>
+      </c>
+    </row>
+    <row r="133" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B133" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C133" t="str">
+        <f t="shared" ref="B133:J133" si="60">_xlfn.CONCAT(C$75,": ",C61, ", ")</f>
+        <v xml:space="preserve">Dw: 0.75, </v>
+      </c>
+      <c r="D133" t="str">
+        <f t="shared" si="60"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E133" t="str">
+        <f t="shared" si="60"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F133" t="str">
+        <f t="shared" si="60"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.99, </v>
+      </c>
+      <c r="G133" t="str">
+        <f t="shared" si="60"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.93, </v>
+      </c>
+      <c r="H133" t="str">
+        <f t="shared" si="60"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.84, </v>
+      </c>
+      <c r="I133" t="str">
+        <f t="shared" si="60"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.7, </v>
+      </c>
+      <c r="J133" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.57}, </v>
+      </c>
+      <c r="L133" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.75, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.99, Fty_E_eu_4: 0.93, Fty_E_eu_6: 0.84, Fty_E_eu_8: 0.7, Fty_E_eu_10: 0.57}, </v>
+      </c>
+    </row>
+    <row r="134" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B134" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C134" t="str">
+        <f t="shared" ref="B134:J134" si="61">_xlfn.CONCAT(C$75,": ",C62, ", ")</f>
+        <v xml:space="preserve">Dw: 0.8, </v>
+      </c>
+      <c r="D134" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E134" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F134" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">Fty_E_eu_2: 1, </v>
+      </c>
+      <c r="G134" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.97, </v>
+      </c>
+      <c r="H134" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.91, </v>
+      </c>
+      <c r="I134" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.76, </v>
+      </c>
+      <c r="J134" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.63}, </v>
+      </c>
+      <c r="L134" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.8, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 1, Fty_E_eu_4: 0.97, Fty_E_eu_6: 0.91, Fty_E_eu_8: 0.76, Fty_E_eu_10: 0.63}, </v>
+      </c>
+    </row>
+    <row r="135" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B135" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C135" t="str">
+        <f t="shared" ref="B135:J135" si="62">_xlfn.CONCAT(C$75,": ",C63, ", ")</f>
+        <v xml:space="preserve">Dw: 0.85, </v>
+      </c>
+      <c r="D135" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E135" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F135" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">Fty_E_eu_2: 0.99, </v>
+      </c>
+      <c r="G135" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">Fty_E_eu_4: 0.99, </v>
+      </c>
+      <c r="H135" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.94, </v>
+      </c>
+      <c r="I135" t="str">
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.81, </v>
+      </c>
+      <c r="J135" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.69}, </v>
+      </c>
+      <c r="L135" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.85, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.99, Fty_E_eu_4: 0.99, Fty_E_eu_6: 0.94, Fty_E_eu_8: 0.81, Fty_E_eu_10: 0.69}, </v>
+      </c>
+    </row>
+    <row r="136" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B136" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C136" t="str">
+        <f t="shared" ref="B136:J136" si="63">_xlfn.CONCAT(C$75,": ",C64, ", ")</f>
+        <v xml:space="preserve">Dw: 0.9, </v>
+      </c>
+      <c r="D136" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E136" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F136" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">Fty_E_eu_2: 1, </v>
+      </c>
+      <c r="G136" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">Fty_E_eu_4: 1, </v>
+      </c>
+      <c r="H136" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.97, </v>
+      </c>
+      <c r="I136" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.86, </v>
+      </c>
+      <c r="J136" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.78}, </v>
+      </c>
+      <c r="L136" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.9, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 1, Fty_E_eu_4: 1, Fty_E_eu_6: 0.97, Fty_E_eu_8: 0.86, Fty_E_eu_10: 0.78}, </v>
+      </c>
+    </row>
+    <row r="137" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B137" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C137" t="str">
+        <f t="shared" ref="B137:J137" si="64">_xlfn.CONCAT(C$75,": ",C65, ", ")</f>
+        <v xml:space="preserve">Dw: 0.95, </v>
+      </c>
+      <c r="D137" t="str">
+        <f t="shared" si="64"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E137" t="str">
+        <f t="shared" si="64"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F137" t="str">
+        <f t="shared" si="64"/>
+        <v xml:space="preserve">Fty_E_eu_2: 1, </v>
+      </c>
+      <c r="G137" t="str">
+        <f t="shared" si="64"/>
+        <v xml:space="preserve">Fty_E_eu_4: 1, </v>
+      </c>
+      <c r="H137" t="str">
+        <f t="shared" si="64"/>
+        <v xml:space="preserve">Fty_E_eu_6: 0.99, </v>
+      </c>
+      <c r="I137" t="str">
+        <f t="shared" si="64"/>
+        <v xml:space="preserve">Fty_E_eu_8: 0.92, </v>
+      </c>
+      <c r="J137" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">Fty_E_eu_10: 0.87}, </v>
+      </c>
+      <c r="L137" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 0.95, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 1, Fty_E_eu_4: 1, Fty_E_eu_6: 0.99, Fty_E_eu_8: 0.92, Fty_E_eu_10: 0.87}, </v>
+      </c>
+    </row>
+    <row r="138" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B138" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, </v>
+      </c>
+      <c r="C138" t="str">
+        <f t="shared" ref="B138:J138" si="65">_xlfn.CONCAT(C$75,": ",C66, ", ")</f>
+        <v xml:space="preserve">Dw: 1, </v>
+      </c>
+      <c r="D138" t="str">
+        <f t="shared" si="65"/>
+        <v xml:space="preserve">Fty_E_eu_0: 1, </v>
+      </c>
+      <c r="E138" t="str">
+        <f t="shared" si="65"/>
+        <v xml:space="preserve">Fty_E_eu_1: 1, </v>
+      </c>
+      <c r="F138" t="str">
+        <f t="shared" si="65"/>
+        <v xml:space="preserve">Fty_E_eu_2: 1, </v>
+      </c>
+      <c r="G138" t="str">
+        <f t="shared" si="65"/>
+        <v xml:space="preserve">Fty_E_eu_4: 1, </v>
+      </c>
+      <c r="H138" t="str">
+        <f t="shared" si="65"/>
+        <v xml:space="preserve">Fty_E_eu_6: 1, </v>
+      </c>
+      <c r="I138" t="str">
+        <f t="shared" si="65"/>
+        <v xml:space="preserve">Fty_E_eu_8: 1, </v>
+      </c>
+      <c r="J138" t="str">
+        <f>_xlfn.CONCAT(J$75,": ",J66, "} ")</f>
+        <v xml:space="preserve">Fty_E_eu_10: 1} </v>
+      </c>
+      <c r="L138" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">{Fty_Ftu: 1, Dw: 1, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 1, Fty_E_eu_4: 1, Fty_E_eu_6: 1, Fty_E_eu_8: 1, Fty_E_eu_10: 1} </v>
+      </c>
+    </row>
+    <row r="141" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L141" t="str">
+        <f>_xlfn.CONCAT("[",L76:L138,"]")</f>
+        <v>[{Fty_Ftu: 0.6, Dw: 0, Fty_E_eu_0: 0, Fty_E_eu_1: 0, Fty_E_eu_2: 0, Fty_E_eu_4: 0, Fty_E_eu_6: 0, Fty_E_eu_8: 0, Fty_E_eu_10: 0}, {Fty_Ftu: 0.6, Dw: 0.05, Fty_E_eu_0: 0.33, Fty_E_eu_1: 0.33, Fty_E_eu_2: 0.26, Fty_E_eu_4: 0.15, Fty_E_eu_6: 0.09, Fty_E_eu_8: 0.07, Fty_E_eu_10: 0.06}, {Fty_Ftu: 0.6, Dw: 0.1, Fty_E_eu_0: 0.5, Fty_E_eu_1: 0.49, Fty_E_eu_2: 0.41, Fty_E_eu_4: 0.24, Fty_E_eu_6: 0.16, Fty_E_eu_8: 0.12, Fty_E_eu_10: 0.1}, {Fty_Ftu: 0.6, Dw: 0.15, Fty_E_eu_0: 0.61, Fty_E_eu_1: 0.58, Fty_E_eu_2: 0.52, Fty_E_eu_4: 0.32, Fty_E_eu_6: 0.22, Fty_E_eu_8: 0.18, Fty_E_eu_10: 0.15}, {Fty_Ftu: 0.6, Dw: 0.2, Fty_E_eu_0: 0.67, Fty_E_eu_1: 0.65, Fty_E_eu_2: 0.59, Fty_E_eu_4: 0.4, Fty_E_eu_6: 0.3, Fty_E_eu_8: 0.24, Fty_E_eu_10: 0.19}, {Fty_Ftu: 0.6, Dw: 0.25, Fty_E_eu_0: 0.7, Fty_E_eu_1: 0.68, Fty_E_eu_2: 0.63, Fty_E_eu_4: 0.47, Fty_E_eu_6: 0.36, Fty_E_eu_8: 0.29, Fty_E_eu_10: 0.24}, {Fty_Ftu: 0.6, Dw: 0.3, Fty_E_eu_0: 0.71, Fty_E_eu_1: 0.69, Fty_E_eu_2: 0.66, Fty_E_eu_4: 0.53, Fty_E_eu_6: 0.41, Fty_E_eu_8: 0.33, Fty_E_eu_10: 0.27}, {Fty_Ftu: 0.6, Dw: 0.35, Fty_E_eu_0: 0.72, Fty_E_eu_1: 0.7, Fty_E_eu_2: 0.68, Fty_E_eu_4: 0.57, Fty_E_eu_6: 0.45, Fty_E_eu_8: 0.37, Fty_E_eu_10: 0.31}, {Fty_Ftu: 0.6, Dw: 0.4, Fty_E_eu_0: 0.73, Fty_E_eu_1: 0.71, Fty_E_eu_2: 0.69, Fty_E_eu_4: 0.61, Fty_E_eu_6: 0.49, Fty_E_eu_8: 0.4, Fty_E_eu_10: 0.34}, {Fty_Ftu: 0.6, Dw: 0.45, Fty_E_eu_0: 0.74, Fty_E_eu_1: 0.72, Fty_E_eu_2: 0.7, Fty_E_eu_4: 0.63, Fty_E_eu_6: 0.53, Fty_E_eu_8: 0.43, Fty_E_eu_10: 0.36}, {Fty_Ftu: 0.6, Dw: 0.5, Fty_E_eu_0: 0.76, Fty_E_eu_1: 0.74, Fty_E_eu_2: 0.72, Fty_E_eu_4: 0.64, Fty_E_eu_6: 0.56, Fty_E_eu_8: 0.46, Fty_E_eu_10: 0.4}, {Fty_Ftu: 0.6, Dw: 0.55, Fty_E_eu_0: 0.77, Fty_E_eu_1: 0.76, Fty_E_eu_2: 0.73, Fty_E_eu_4: 0.66, Fty_E_eu_6: 0.59, Fty_E_eu_8: 0.5, Fty_E_eu_10: 0.43}, {Fty_Ftu: 0.6, Dw: 0.6, Fty_E_eu_0: 0.78, Fty_E_eu_1: 0.77, Fty_E_eu_2: 0.74, Fty_E_eu_4: 0.68, Fty_E_eu_6: 0.62, Fty_E_eu_8: 0.53, Fty_E_eu_10: 0.45}, {Fty_Ftu: 0.6, Dw: 0.65, Fty_E_eu_0: 0.8, Fty_E_eu_1: 0.79, Fty_E_eu_2: 0.77, Fty_E_eu_4: 0.7, Fty_E_eu_6: 0.64, Fty_E_eu_8: 0.57, Fty_E_eu_10: 0.49}, {Fty_Ftu: 0.6, Dw: 0.7, Fty_E_eu_0: 0.82, Fty_E_eu_1: 0.81, Fty_E_eu_2: 0.78, Fty_E_eu_4: 0.73, Fty_E_eu_6: 0.68, Fty_E_eu_8: 0.61, Fty_E_eu_10: 0.53}, {Fty_Ftu: 0.6, Dw: 0.75, Fty_E_eu_0: 0.84, Fty_E_eu_1: 0.82, Fty_E_eu_2: 0.81, Fty_E_eu_4: 0.77, Fty_E_eu_6: 0.72, Fty_E_eu_8: 0.66, Fty_E_eu_10: 0.58}, {Fty_Ftu: 0.6, Dw: 0.8, Fty_E_eu_0: 0.86, Fty_E_eu_1: 0.84, Fty_E_eu_2: 0.84, Fty_E_eu_4: 0.8, Fty_E_eu_6: 0.76, Fty_E_eu_8: 0.71, Fty_E_eu_10: 0.64}, {Fty_Ftu: 0.6, Dw: 0.85, Fty_E_eu_0: 0.88, Fty_E_eu_1: 0.87, Fty_E_eu_2: 0.87, Fty_E_eu_4: 0.84, Fty_E_eu_6: 0.81, Fty_E_eu_8: 0.77, Fty_E_eu_10: 0.71}, {Fty_Ftu: 0.6, Dw: 0.9, Fty_E_eu_0: 0.91, Fty_E_eu_1: 0.9, Fty_E_eu_2: 0.9, Fty_E_eu_4: 0.88, Fty_E_eu_6: 0.86, Fty_E_eu_8: 0.83, Fty_E_eu_10: 0.79}, {Fty_Ftu: 0.6, Dw: 0.95, Fty_E_eu_0: 0.95, Fty_E_eu_1: 0.95, Fty_E_eu_2: 0.95, Fty_E_eu_4: 0.94, Fty_E_eu_6: 0.94, Fty_E_eu_8: 0.92, Fty_E_eu_10: 0.89}, {Fty_Ftu: 0.6, Dw: 1, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 1, Fty_E_eu_4: 1, Fty_E_eu_6: 1, Fty_E_eu_8: 1, Fty_E_eu_10: 1}, {Fty_Ftu: 0.8, Dw: 0, Fty_E_eu_0: 0, Fty_E_eu_1: 0, Fty_E_eu_2: 0, Fty_E_eu_4: 0, Fty_E_eu_6: 0, Fty_E_eu_8: 0, Fty_E_eu_10: 0}, {Fty_Ftu: 0.8, Dw: 0.05, Fty_E_eu_0: 0.4, Fty_E_eu_1: 0.38, Fty_E_eu_2: 0.24, Fty_E_eu_4: 0.14, Fty_E_eu_6: 0.08, Fty_E_eu_8: 0.07, Fty_E_eu_10: 0.05}, {Fty_Ftu: 0.8, Dw: 0.1, Fty_E_eu_0: 0.66, Fty_E_eu_1: 0.59, Fty_E_eu_2: 0.42, Fty_E_eu_4: 0.25, Fty_E_eu_6: 0.15, Fty_E_eu_8: 0.12, Fty_E_eu_10: 0.1}, {Fty_Ftu: 0.8, Dw: 0.15, Fty_E_eu_0: 0.79, Fty_E_eu_1: 0.73, Fty_E_eu_2: 0.56, Fty_E_eu_4: 0.35, Fty_E_eu_6: 0.22, Fty_E_eu_8: 0.18, Fty_E_eu_10: 0.15}, {Fty_Ftu: 0.8, Dw: 0.2, Fty_E_eu_0: 0.83, Fty_E_eu_1: 0.81, Fty_E_eu_2: 0.67, Fty_E_eu_4: 0.43, Fty_E_eu_6: 0.29, Fty_E_eu_8: 0.23, Fty_E_eu_10: 0.19}, {Fty_Ftu: 0.8, Dw: 0.25, Fty_E_eu_0: 0.84, Fty_E_eu_1: 0.83, Fty_E_eu_2: 0.74, Fty_E_eu_4: 0.5, Fty_E_eu_6: 0.36, Fty_E_eu_8: 0.28, Fty_E_eu_10: 0.24}, {Fty_Ftu: 0.8, Dw: 0.3, Fty_E_eu_0: 0.85, Fty_E_eu_1: 0.84, Fty_E_eu_2: 0.77, Fty_E_eu_4: 0.56, Fty_E_eu_6: 0.42, Fty_E_eu_8: 0.33, Fty_E_eu_10: 0.28}, {Fty_Ftu: 0.8, Dw: 0.35, Fty_E_eu_0: 0.85, Fty_E_eu_1: 0.85, Fty_E_eu_2: 0.8, Fty_E_eu_4: 0.62, Fty_E_eu_6: 0.48, Fty_E_eu_8: 0.37, Fty_E_eu_10: 0.31}, {Fty_Ftu: 0.8, Dw: 0.4, Fty_E_eu_0: 0.86, Fty_E_eu_1: 0.86, Fty_E_eu_2: 0.81, Fty_E_eu_4: 0.66, Fty_E_eu_6: 0.52, Fty_E_eu_8: 0.41, Fty_E_eu_10: 0.34}, {Fty_Ftu: 0.8, Dw: 0.45, Fty_E_eu_0: 0.86, Fty_E_eu_1: 0.86, Fty_E_eu_2: 0.83, Fty_E_eu_4: 0.69, Fty_E_eu_6: 0.56, Fty_E_eu_8: 0.44, Fty_E_eu_10: 0.37}, {Fty_Ftu: 0.8, Dw: 0.5, Fty_E_eu_0: 0.87, Fty_E_eu_1: 0.87, Fty_E_eu_2: 0.84, Fty_E_eu_4: 0.72, Fty_E_eu_6: 0.59, Fty_E_eu_8: 0.47, Fty_E_eu_10: 0.4}, {Fty_Ftu: 0.8, Dw: 0.55, Fty_E_eu_0: 0.88, Fty_E_eu_1: 0.88, Fty_E_eu_2: 0.84, Fty_E_eu_4: 0.74, Fty_E_eu_6: 0.62, Fty_E_eu_8: 0.51, Fty_E_eu_10: 0.44}, {Fty_Ftu: 0.8, Dw: 0.6, Fty_E_eu_0: 0.89, Fty_E_eu_1: 0.89, Fty_E_eu_2: 0.85, Fty_E_eu_4: 0.76, Fty_E_eu_6: 0.65, Fty_E_eu_8: 0.55, Fty_E_eu_10: 0.47}, {Fty_Ftu: 0.8, Dw: 0.65, Fty_E_eu_0: 0.9, Fty_E_eu_1: 0.9, Fty_E_eu_2: 0.86, Fty_E_eu_4: 0.79, Fty_E_eu_6: 0.68, Fty_E_eu_8: 0.58, Fty_E_eu_10: 0.5}, {Fty_Ftu: 0.8, Dw: 0.7, Fty_E_eu_0: 0.9, Fty_E_eu_1: 0.9, Fty_E_eu_2: 0.87, Fty_E_eu_4: 0.82, Fty_E_eu_6: 0.72, Fty_E_eu_8: 0.63, Fty_E_eu_10: 0.53}, {Fty_Ftu: 0.8, Dw: 0.75, Fty_E_eu_0: 0.91, Fty_E_eu_1: 0.91, Fty_E_eu_2: 0.89, Fty_E_eu_4: 0.84, Fty_E_eu_6: 0.77, Fty_E_eu_8: 0.69, Fty_E_eu_10: 0.58}, {Fty_Ftu: 0.8, Dw: 0.8, Fty_E_eu_0: 0.92, Fty_E_eu_1: 0.92, Fty_E_eu_2: 0.92, Fty_E_eu_4: 0.88, Fty_E_eu_6: 0.83, Fty_E_eu_8: 0.74, Fty_E_eu_10: 0.64}, {Fty_Ftu: 0.8, Dw: 0.85, Fty_E_eu_0: 0.94, Fty_E_eu_1: 0.94, Fty_E_eu_2: 0.94, Fty_E_eu_4: 0.91, Fty_E_eu_6: 0.87, Fty_E_eu_8: 0.79, Fty_E_eu_10: 0.71}, {Fty_Ftu: 0.8, Dw: 0.9, Fty_E_eu_0: 0.96, Fty_E_eu_1: 0.96, Fty_E_eu_2: 0.96, Fty_E_eu_4: 0.94, Fty_E_eu_6: 0.91, Fty_E_eu_8: 0.85, Fty_E_eu_10: 0.79}, {Fty_Ftu: 0.8, Dw: 0.95, Fty_E_eu_0: 0.97, Fty_E_eu_1: 0.97, Fty_E_eu_2: 0.97, Fty_E_eu_4: 0.97, Fty_E_eu_6: 0.95, Fty_E_eu_8: 0.92, Fty_E_eu_10: 0.88}, {Fty_Ftu: 0.8, Dw: 1, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 1, Fty_E_eu_4: 1, Fty_E_eu_6: 1, Fty_E_eu_8: 1, Fty_E_eu_10: 1}, {Fty_Ftu: 1, Dw: 0, Fty_E_eu_0: 0, Fty_E_eu_1: 0, Fty_E_eu_2: 0, Fty_E_eu_4: 0, Fty_E_eu_6: 0, Fty_E_eu_8: 0, Fty_E_eu_10: 0}, {Fty_Ftu: 1, Dw: 0.05, Fty_E_eu_0: 0.54, Fty_E_eu_1: 0.44, Fty_E_eu_2: 0.26, Fty_E_eu_4: 0.13, Fty_E_eu_6: 0.09, Fty_E_eu_8: 0.07, Fty_E_eu_10: 0.06}, {Fty_Ftu: 1, Dw: 0.1, Fty_E_eu_0: 0.78, Fty_E_eu_1: 0.69, Fty_E_eu_2: 0.44, Fty_E_eu_4: 0.22, Fty_E_eu_6: 0.16, Fty_E_eu_8: 0.13, Fty_E_eu_10: 0.12}, {Fty_Ftu: 1, Dw: 0.15, Fty_E_eu_0: 0.93, Fty_E_eu_1: 0.86, Fty_E_eu_2: 0.58, Fty_E_eu_4: 0.31, Fty_E_eu_6: 0.23, Fty_E_eu_8: 0.18, Fty_E_eu_10: 0.16}, {Fty_Ftu: 1, Dw: 0.2, Fty_E_eu_0: 1, Fty_E_eu_1: 0.96, Fty_E_eu_2: 0.71, Fty_E_eu_4: 0.42, Fty_E_eu_6: 0.3, Fty_E_eu_8: 0.23, Fty_E_eu_10: 0.2}, {Fty_Ftu: 1, Dw: 0.25, Fty_E_eu_0: 1, Fty_E_eu_1: 0.98, Fty_E_eu_2: 0.8, Fty_E_eu_4: 0.5, Fty_E_eu_6: 0.36, Fty_E_eu_8: 0.28, Fty_E_eu_10: 0.24}, {Fty_Ftu: 1, Dw: 0.3, Fty_E_eu_0: 1, Fty_E_eu_1: 0.99, Fty_E_eu_2: 0.87, Fty_E_eu_4: 0.6, Fty_E_eu_6: 0.42, Fty_E_eu_8: 0.33, Fty_E_eu_10: 0.28}, {Fty_Ftu: 1, Dw: 0.35, Fty_E_eu_0: 1, Fty_E_eu_1: 0.99, Fty_E_eu_2: 0.93, Fty_E_eu_4: 0.66, Fty_E_eu_6: 0.48, Fty_E_eu_8: 0.37, Fty_E_eu_10: 0.31}, {Fty_Ftu: 1, Dw: 0.4, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.96, Fty_E_eu_4: 0.71, Fty_E_eu_6: 0.53, Fty_E_eu_8: 0.41, Fty_E_eu_10: 0.34}, {Fty_Ftu: 1, Dw: 0.45, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.97, Fty_E_eu_4: 0.75, Fty_E_eu_6: 0.58, Fty_E_eu_8: 0.45, Fty_E_eu_10: 0.37}, {Fty_Ftu: 1, Dw: 0.5, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.96, Fty_E_eu_4: 0.78, Fty_E_eu_6: 0.62, Fty_E_eu_8: 0.49, Fty_E_eu_10: 0.4}, {Fty_Ftu: 1, Dw: 0.55, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.96, Fty_E_eu_4: 0.8, Fty_E_eu_6: 0.66, Fty_E_eu_8: 0.53, Fty_E_eu_10: 0.43}, {Fty_Ftu: 1, Dw: 0.6, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.96, Fty_E_eu_4: 0.83, Fty_E_eu_6: 0.69, Fty_E_eu_8: 0.56, Fty_E_eu_10: 0.46}, {Fty_Ftu: 1, Dw: 0.65, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.96, Fty_E_eu_4: 0.87, Fty_E_eu_6: 0.73, Fty_E_eu_8: 0.6, Fty_E_eu_10: 0.5}, {Fty_Ftu: 1, Dw: 0.7, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.97, Fty_E_eu_4: 0.9, Fty_E_eu_6: 0.78, Fty_E_eu_8: 0.64, Fty_E_eu_10: 0.53}, {Fty_Ftu: 1, Dw: 0.75, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.99, Fty_E_eu_4: 0.93, Fty_E_eu_6: 0.84, Fty_E_eu_8: 0.7, Fty_E_eu_10: 0.57}, {Fty_Ftu: 1, Dw: 0.8, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 1, Fty_E_eu_4: 0.97, Fty_E_eu_6: 0.91, Fty_E_eu_8: 0.76, Fty_E_eu_10: 0.63}, {Fty_Ftu: 1, Dw: 0.85, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 0.99, Fty_E_eu_4: 0.99, Fty_E_eu_6: 0.94, Fty_E_eu_8: 0.81, Fty_E_eu_10: 0.69}, {Fty_Ftu: 1, Dw: 0.9, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 1, Fty_E_eu_4: 1, Fty_E_eu_6: 0.97, Fty_E_eu_8: 0.86, Fty_E_eu_10: 0.78}, {Fty_Ftu: 1, Dw: 0.95, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 1, Fty_E_eu_4: 1, Fty_E_eu_6: 0.99, Fty_E_eu_8: 0.92, Fty_E_eu_10: 0.87}, {Fty_Ftu: 1, Dw: 1, Fty_E_eu_0: 1, Fty_E_eu_1: 1, Fty_E_eu_2: 1, Fty_E_eu_4: 1, Fty_E_eu_6: 1, Fty_E_eu_8: 1, Fty_E_eu_10: 1} ]</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>